--- a/data/3FEB_25_26/clutch_aggregated_25_26_3FEB.xlsx
+++ b/data/3FEB_25_26/clutch_aggregated_25_26_3FEB.xlsx
@@ -4007,67 +4007,67 @@
         </is>
       </c>
       <c r="C48" t="n">
+        <v>11</v>
+      </c>
+      <c r="D48" t="n">
+        <v>31.87</v>
+      </c>
+      <c r="E48" t="n">
+        <v>1912.2</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" t="n">
         <v>10</v>
-      </c>
-      <c r="D48" t="n">
-        <v>29.17</v>
-      </c>
-      <c r="E48" t="n">
-        <v>1750.2</v>
-      </c>
-      <c r="F48" t="n">
-        <v>0</v>
-      </c>
-      <c r="G48" t="n">
-        <v>9</v>
       </c>
       <c r="H48" t="n">
         <v>5</v>
       </c>
       <c r="I48" t="n">
+        <v>8</v>
+      </c>
+      <c r="J48" t="n">
+        <v>3</v>
+      </c>
+      <c r="K48" t="n">
+        <v>1</v>
+      </c>
+      <c r="L48" t="n">
+        <v>1</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="N48" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>2</v>
+      </c>
+      <c r="R48" t="n">
+        <v>8</v>
+      </c>
+      <c r="S48" t="n">
+        <v>3</v>
+      </c>
+      <c r="T48" t="n">
+        <v>5</v>
+      </c>
+      <c r="U48" t="n">
+        <v>16.7355820520866</v>
+      </c>
+      <c r="V48" t="n">
         <v>7</v>
       </c>
-      <c r="J48" t="n">
-        <v>3</v>
-      </c>
-      <c r="K48" t="n">
-        <v>1</v>
-      </c>
-      <c r="L48" t="n">
-        <v>1</v>
-      </c>
-      <c r="M48" t="n">
-        <v>0.7222222222222222</v>
-      </c>
-      <c r="N48" t="n">
-        <v>0</v>
-      </c>
-      <c r="O48" t="n">
-        <v>0</v>
-      </c>
-      <c r="P48" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>2</v>
-      </c>
-      <c r="R48" t="n">
-        <v>7</v>
-      </c>
-      <c r="S48" t="n">
-        <v>3</v>
-      </c>
-      <c r="T48" t="n">
-        <v>4</v>
-      </c>
-      <c r="U48" t="n">
-        <v>16.33993829276654</v>
-      </c>
-      <c r="V48" t="n">
-        <v>12</v>
-      </c>
       <c r="W48" t="n">
-        <v>11.5597188892698</v>
+        <v>-2.416379039849387</v>
       </c>
     </row>
     <row r="49">
@@ -4082,13 +4082,13 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D49" t="n">
-        <v>0.05</v>
+        <v>2.25</v>
       </c>
       <c r="E49" t="n">
-        <v>3</v>
+        <v>135</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -4121,28 +4121,28 @@
         <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U49" t="n">
-        <v>0</v>
+        <v>25.19733333333333</v>
       </c>
       <c r="V49" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
       <c r="W49" t="n">
-        <v>0</v>
+        <v>-145.3466666666667</v>
       </c>
     </row>
     <row r="50">
@@ -4232,13 +4232,13 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D51" t="n">
-        <v>33.37</v>
+        <v>36.07</v>
       </c>
       <c r="E51" t="n">
-        <v>2002.2</v>
+        <v>2164.2</v>
       </c>
       <c r="F51" t="n">
         <v>0</v>
@@ -4256,10 +4256,10 @@
         <v>4</v>
       </c>
       <c r="K51" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="L51" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M51" t="n">
         <v>0.5</v>
@@ -4271,7 +4271,7 @@
         <v>6</v>
       </c>
       <c r="P51" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q51" t="n">
         <v>2</v>
@@ -4286,13 +4286,13 @@
         <v>2</v>
       </c>
       <c r="U51" t="n">
-        <v>34.30365897512736</v>
+        <v>34.69262822289992</v>
       </c>
       <c r="V51" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="W51" t="n">
-        <v>13.75100389571472</v>
+        <v>1.23825894094816</v>
       </c>
     </row>
     <row r="52">
@@ -4532,13 +4532,13 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D55" t="n">
-        <v>17.58</v>
+        <v>18.73</v>
       </c>
       <c r="E55" t="n">
-        <v>1054.8</v>
+        <v>1123.8</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -4586,13 +4586,13 @@
         <v>3</v>
       </c>
       <c r="U55" t="n">
-        <v>28.70343572241184</v>
+        <v>26.94107848371597</v>
       </c>
       <c r="V55" t="n">
-        <v>-6</v>
+        <v>-8</v>
       </c>
       <c r="W55" t="n">
-        <v>-2.453202502844144</v>
+        <v>-8.117047517351844</v>
       </c>
     </row>
     <row r="56">
@@ -4607,13 +4607,13 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D56" t="n">
-        <v>4.880000000000001</v>
+        <v>5.380000000000001</v>
       </c>
       <c r="E56" t="n">
-        <v>292.8</v>
+        <v>322.8</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -4667,7 +4667,7 @@
         <v>1</v>
       </c>
       <c r="W56" t="n">
-        <v>49.5580737704918</v>
+        <v>44.95230483271376</v>
       </c>
     </row>
     <row r="57">
@@ -4682,13 +4682,13 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D57" t="n">
-        <v>17.41</v>
+        <v>17.91</v>
       </c>
       <c r="E57" t="n">
-        <v>1044.6</v>
+        <v>1074.6</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -4706,7 +4706,7 @@
         <v>1</v>
       </c>
       <c r="K57" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
@@ -4736,13 +4736,13 @@
         <v>1</v>
       </c>
       <c r="U57" t="n">
-        <v>10.18131533601379</v>
+        <v>12.68881630374093</v>
       </c>
       <c r="V57" t="n">
         <v>-4</v>
       </c>
       <c r="W57" t="n">
-        <v>-25.38288914417002</v>
+        <v>-24.674265773311</v>
       </c>
     </row>
     <row r="58">
@@ -4757,13 +4757,13 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D58" t="n">
-        <v>33.45</v>
+        <v>35.65</v>
       </c>
       <c r="E58" t="n">
-        <v>2007</v>
+        <v>2139</v>
       </c>
       <c r="F58" t="n">
         <v>0</v>
@@ -4811,13 +4811,13 @@
         <v>2</v>
       </c>
       <c r="U58" t="n">
-        <v>24.27728550074739</v>
+        <v>22.7791079943899</v>
       </c>
       <c r="V58" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W58" t="n">
-        <v>3.294364723467865</v>
+        <v>-6.08228611500701</v>
       </c>
     </row>
     <row r="59">
@@ -4832,19 +4832,19 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D59" t="n">
-        <v>4.58</v>
+        <v>6.13</v>
       </c>
       <c r="E59" t="n">
-        <v>274.8</v>
+        <v>367.8</v>
       </c>
       <c r="F59" t="n">
         <v>0</v>
       </c>
       <c r="G59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H59" t="n">
         <v>1</v>
@@ -4862,7 +4862,7 @@
         <v>1</v>
       </c>
       <c r="M59" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="N59" t="n">
         <v>0</v>
@@ -4886,13 +4886,13 @@
         <v>0</v>
       </c>
       <c r="U59" t="n">
-        <v>27.93668122270742</v>
+        <v>27.38882544861338</v>
       </c>
       <c r="V59" t="n">
-        <v>-2</v>
+        <v>-5</v>
       </c>
       <c r="W59" t="n">
-        <v>-99.0589519650655</v>
+        <v>-111.9396411092985</v>
       </c>
     </row>
     <row r="60">
@@ -12032,67 +12032,67 @@
         </is>
       </c>
       <c r="C155" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D155" t="n">
-        <v>27.18</v>
+        <v>29.88</v>
       </c>
       <c r="E155" t="n">
-        <v>1630.8</v>
+        <v>1792.8</v>
       </c>
       <c r="F155" t="n">
         <v>0</v>
       </c>
       <c r="G155" t="n">
+        <v>8</v>
+      </c>
+      <c r="H155" t="n">
+        <v>2</v>
+      </c>
+      <c r="I155" t="n">
+        <v>6</v>
+      </c>
+      <c r="J155" t="n">
+        <v>0</v>
+      </c>
+      <c r="K155" t="n">
+        <v>3</v>
+      </c>
+      <c r="L155" t="n">
+        <v>3</v>
+      </c>
+      <c r="M155" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="N155" t="n">
+        <v>0</v>
+      </c>
+      <c r="O155" t="n">
+        <v>2</v>
+      </c>
+      <c r="P155" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q155" t="n">
+        <v>2</v>
+      </c>
+      <c r="R155" t="n">
         <v>7</v>
       </c>
-      <c r="H155" t="n">
-        <v>2</v>
-      </c>
-      <c r="I155" t="n">
-        <v>5</v>
-      </c>
-      <c r="J155" t="n">
-        <v>0</v>
-      </c>
-      <c r="K155" t="n">
-        <v>3</v>
-      </c>
-      <c r="L155" t="n">
-        <v>3</v>
-      </c>
-      <c r="M155" t="n">
-        <v>0.2857142857142857</v>
-      </c>
-      <c r="N155" t="n">
-        <v>0</v>
-      </c>
-      <c r="O155" t="n">
-        <v>2</v>
-      </c>
-      <c r="P155" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q155" t="n">
-        <v>2</v>
-      </c>
-      <c r="R155" t="n">
-        <v>6</v>
-      </c>
       <c r="S155" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T155" t="n">
         <v>4</v>
       </c>
       <c r="U155" t="n">
-        <v>21.35193524650479</v>
+        <v>22.04935073627845</v>
       </c>
       <c r="V155" t="n">
-        <v>-4</v>
+        <v>1</v>
       </c>
       <c r="W155" t="n">
-        <v>10.43743929359824</v>
+        <v>23.35664658634538</v>
       </c>
     </row>
     <row r="156">
@@ -12107,28 +12107,28 @@
         </is>
       </c>
       <c r="C156" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D156" t="n">
-        <v>8.52</v>
+        <v>11.22</v>
       </c>
       <c r="E156" t="n">
-        <v>511.2</v>
+        <v>673.2</v>
       </c>
       <c r="F156" t="n">
         <v>0</v>
       </c>
       <c r="G156" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H156" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I156" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J156" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K156" t="n">
         <v>2</v>
@@ -12137,7 +12137,7 @@
         <v>1</v>
       </c>
       <c r="M156" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="N156" t="n">
         <v>0</v>
@@ -12152,22 +12152,22 @@
         <v>1</v>
       </c>
       <c r="R156" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S156" t="n">
         <v>1</v>
       </c>
       <c r="T156" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U156" t="n">
-        <v>32.9574882629108</v>
+        <v>39.01745098039216</v>
       </c>
       <c r="V156" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W156" t="n">
-        <v>17.43692488262911</v>
+        <v>50.1577183600713</v>
       </c>
     </row>
     <row r="157">
@@ -12332,13 +12332,13 @@
         </is>
       </c>
       <c r="C159" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D159" t="n">
-        <v>31.49</v>
+        <v>34.19</v>
       </c>
       <c r="E159" t="n">
-        <v>1889.4</v>
+        <v>2051.4</v>
       </c>
       <c r="F159" t="n">
         <v>0</v>
@@ -12374,25 +12374,25 @@
         <v>2</v>
       </c>
       <c r="Q159" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R159" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="S159" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="T159" t="n">
         <v>4</v>
       </c>
       <c r="U159" t="n">
-        <v>32.96378215306446</v>
+        <v>30.36061713951448</v>
       </c>
       <c r="V159" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="W159" t="n">
-        <v>11.71023181962528</v>
+        <v>22.90032758116408</v>
       </c>
     </row>
     <row r="160">
@@ -12482,67 +12482,67 @@
         </is>
       </c>
       <c r="C161" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D161" t="n">
-        <v>12.18</v>
+        <v>14.88</v>
       </c>
       <c r="E161" t="n">
-        <v>730.8</v>
+        <v>892.8</v>
       </c>
       <c r="F161" t="n">
         <v>0</v>
       </c>
       <c r="G161" t="n">
+        <v>10</v>
+      </c>
+      <c r="H161" t="n">
+        <v>3</v>
+      </c>
+      <c r="I161" t="n">
+        <v>4</v>
+      </c>
+      <c r="J161" t="n">
+        <v>0</v>
+      </c>
+      <c r="K161" t="n">
+        <v>8</v>
+      </c>
+      <c r="L161" t="n">
+        <v>7</v>
+      </c>
+      <c r="M161" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="N161" t="n">
+        <v>0</v>
+      </c>
+      <c r="O161" t="n">
+        <v>1</v>
+      </c>
+      <c r="P161" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q161" t="n">
+        <v>3</v>
+      </c>
+      <c r="R161" t="n">
+        <v>2</v>
+      </c>
+      <c r="S161" t="n">
+        <v>1</v>
+      </c>
+      <c r="T161" t="n">
+        <v>1</v>
+      </c>
+      <c r="U161" t="n">
+        <v>55.41617607526882</v>
+      </c>
+      <c r="V161" t="n">
         <v>9</v>
       </c>
-      <c r="H161" t="n">
-        <v>2</v>
-      </c>
-      <c r="I161" t="n">
-        <v>4</v>
-      </c>
-      <c r="J161" t="n">
-        <v>0</v>
-      </c>
-      <c r="K161" t="n">
-        <v>7</v>
-      </c>
-      <c r="L161" t="n">
-        <v>6</v>
-      </c>
-      <c r="M161" t="n">
-        <v>0.2222222222222222</v>
-      </c>
-      <c r="N161" t="n">
-        <v>0</v>
-      </c>
-      <c r="O161" t="n">
-        <v>1</v>
-      </c>
-      <c r="P161" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q161" t="n">
-        <v>3</v>
-      </c>
-      <c r="R161" t="n">
-        <v>2</v>
-      </c>
-      <c r="S161" t="n">
-        <v>1</v>
-      </c>
-      <c r="T161" t="n">
-        <v>1</v>
-      </c>
-      <c r="U161" t="n">
-        <v>58.42123973727422</v>
-      </c>
-      <c r="V161" t="n">
-        <v>4</v>
-      </c>
       <c r="W161" t="n">
-        <v>17.86641215106732</v>
+        <v>42.46101478494624</v>
       </c>
     </row>
     <row r="162">
@@ -12632,19 +12632,19 @@
         </is>
       </c>
       <c r="C163" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D163" t="n">
-        <v>22.73</v>
+        <v>24.01</v>
       </c>
       <c r="E163" t="n">
-        <v>1363.8</v>
+        <v>1440.6</v>
       </c>
       <c r="F163" t="n">
         <v>0</v>
       </c>
       <c r="G163" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H163" t="n">
         <v>4</v>
@@ -12662,7 +12662,7 @@
         <v>3</v>
       </c>
       <c r="M163" t="n">
-        <v>0.4</v>
+        <v>0.3636363636363636</v>
       </c>
       <c r="N163" t="n">
         <v>0</v>
@@ -12686,13 +12686,13 @@
         <v>0</v>
       </c>
       <c r="U163" t="n">
-        <v>35.36997800263968</v>
+        <v>33.48436484798001</v>
       </c>
       <c r="V163" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W163" t="n">
-        <v>21.20308402991641</v>
+        <v>20.07272386505623</v>
       </c>
     </row>
     <row r="164">
@@ -12932,19 +12932,19 @@
         </is>
       </c>
       <c r="C167" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D167" t="n">
-        <v>11.8</v>
+        <v>13.22</v>
       </c>
       <c r="E167" t="n">
-        <v>708</v>
+        <v>793.2</v>
       </c>
       <c r="F167" t="n">
         <v>0</v>
       </c>
       <c r="G167" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H167" t="n">
         <v>1</v>
@@ -12962,19 +12962,19 @@
         <v>0</v>
       </c>
       <c r="M167" t="n">
-        <v>0.125</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="N167" t="n">
         <v>0</v>
       </c>
       <c r="O167" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P167" t="n">
         <v>1</v>
       </c>
       <c r="Q167" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R167" t="n">
         <v>3</v>
@@ -12986,13 +12986,13 @@
         <v>1</v>
       </c>
       <c r="U167" t="n">
-        <v>44.45210169491526</v>
+        <v>42.79986384266263</v>
       </c>
       <c r="V167" t="n">
-        <v>-5</v>
+        <v>1</v>
       </c>
       <c r="W167" t="n">
-        <v>-2.724491525423729</v>
+        <v>16.30313161875945</v>
       </c>
     </row>
   </sheetData>

--- a/data/3FEB_25_26/clutch_aggregated_25_26_3FEB.xlsx
+++ b/data/3FEB_25_26/clutch_aggregated_25_26_3FEB.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W170"/>
+  <dimension ref="A1:W171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -557,22 +557,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D2" t="n">
-        <v>54.37</v>
+        <v>55.92</v>
       </c>
       <c r="E2" t="n">
-        <v>3262.2</v>
+        <v>3355.2</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I2" t="n">
         <v>14</v>
@@ -581,13 +581,13 @@
         <v>7</v>
       </c>
       <c r="K2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L2" t="n">
         <v>3</v>
       </c>
       <c r="M2" t="n">
-        <v>0.5869565217391305</v>
+        <v>0.6041666666666666</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
@@ -611,13 +611,13 @@
         <v>2</v>
       </c>
       <c r="U2" t="n">
-        <v>25.02238734596285</v>
+        <v>26.13825464949928</v>
       </c>
       <c r="V2" t="n">
-        <v>-26</v>
+        <v>-28</v>
       </c>
       <c r="W2" t="n">
-        <v>-29.00262460915946</v>
+        <v>-29.89258226037196</v>
       </c>
     </row>
     <row r="3">
@@ -632,37 +632,37 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D3" t="n">
-        <v>72.26000000000001</v>
+        <v>76.26000000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>4335.6</v>
+        <v>4575.6</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H3" t="n">
         <v>8</v>
       </c>
       <c r="I3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J3" t="n">
         <v>4</v>
       </c>
       <c r="K3" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="L3" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.4</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
         <v>3</v>
       </c>
       <c r="R3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="S3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T3" t="n">
         <v>3</v>
       </c>
       <c r="U3" t="n">
-        <v>31.91256850262939</v>
+        <v>31.60821138211382</v>
       </c>
       <c r="V3" t="n">
-        <v>-35</v>
+        <v>-34</v>
       </c>
       <c r="W3" t="n">
-        <v>-22.15895792969832</v>
+        <v>-20.50519669551535</v>
       </c>
     </row>
     <row r="4">
@@ -707,13 +707,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D4" t="n">
-        <v>27.4</v>
+        <v>29.85</v>
       </c>
       <c r="E4" t="n">
-        <v>1644</v>
+        <v>1791</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -752,22 +752,22 @@
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S4" t="n">
         <v>3</v>
       </c>
       <c r="T4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U4" t="n">
-        <v>26.42593065693431</v>
+        <v>24.25696817420435</v>
       </c>
       <c r="V4" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>-8.030905109489053</v>
+        <v>-1.887363484087104</v>
       </c>
     </row>
     <row r="5">
@@ -782,13 +782,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>35.6</v>
+        <v>36.28</v>
       </c>
       <c r="E5" t="n">
-        <v>2136</v>
+        <v>2176.8</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -836,13 +836,13 @@
         <v>3</v>
       </c>
       <c r="U5" t="n">
-        <v>19.27805617977528</v>
+        <v>18.91672546857773</v>
       </c>
       <c r="V5" t="n">
         <v>-27</v>
       </c>
       <c r="W5" t="n">
-        <v>-37.38217415730337</v>
+        <v>-36.68151598676957</v>
       </c>
     </row>
     <row r="6">
@@ -1007,13 +1007,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D8" t="n">
-        <v>41.44</v>
+        <v>45.44</v>
       </c>
       <c r="E8" t="n">
-        <v>2486.4</v>
+        <v>2726.4</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -1046,28 +1046,28 @@
         <v>1</v>
       </c>
       <c r="P8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q8" t="n">
         <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="S8" t="n">
         <v>6</v>
       </c>
       <c r="T8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U8" t="n">
-        <v>28.53342422779923</v>
+        <v>27.24439040492958</v>
       </c>
       <c r="V8" t="n">
-        <v>-16</v>
+        <v>-15</v>
       </c>
       <c r="W8" t="n">
-        <v>-17.23287403474904</v>
+        <v>-14.89107174295775</v>
       </c>
     </row>
     <row r="9">
@@ -1307,22 +1307,22 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>2.63</v>
+        <v>6.63</v>
       </c>
       <c r="E12" t="n">
-        <v>157.8</v>
+        <v>397.8</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -1331,13 +1331,13 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1346,7 +1346,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -1361,13 +1361,13 @@
         <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>25</v>
+        <v>38.74358974358975</v>
       </c>
       <c r="V12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="W12" t="n">
-        <v>98.45</v>
+        <v>44.70641025641026</v>
       </c>
     </row>
     <row r="13">
@@ -1457,13 +1457,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D14" t="n">
-        <v>38.82</v>
+        <v>42.14</v>
       </c>
       <c r="E14" t="n">
-        <v>2329.2</v>
+        <v>2528.4</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -1493,7 +1493,7 @@
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P14" t="n">
         <v>4</v>
@@ -1511,13 +1511,13 @@
         <v>2</v>
       </c>
       <c r="U14" t="n">
-        <v>15.69006955177743</v>
+        <v>14.45392738490745</v>
       </c>
       <c r="V14" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="W14" t="n">
-        <v>0.8094461617722786</v>
+        <v>4.8503725676317</v>
       </c>
     </row>
     <row r="15">
@@ -2507,13 +2507,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D28" t="n">
-        <v>10.62</v>
+        <v>12.8</v>
       </c>
       <c r="E28" t="n">
-        <v>637.2</v>
+        <v>768</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
@@ -2561,13 +2561,13 @@
         <v>1</v>
       </c>
       <c r="U28" t="n">
-        <v>25.05829566854991</v>
+        <v>20.7905546875</v>
       </c>
       <c r="V28" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="W28" t="n">
-        <v>70.38310734463276</v>
+        <v>52.64112500000001</v>
       </c>
     </row>
     <row r="29">
@@ -2582,19 +2582,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D29" t="n">
-        <v>30.08</v>
+        <v>32.26</v>
       </c>
       <c r="E29" t="n">
-        <v>1804.8</v>
+        <v>1935.6</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H29" t="n">
         <v>2</v>
@@ -2606,13 +2606,13 @@
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M29" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
@@ -2636,13 +2636,13 @@
         <v>2</v>
       </c>
       <c r="U29" t="n">
-        <v>12.22441821808511</v>
+        <v>14.13651890886547</v>
       </c>
       <c r="V29" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="W29" t="n">
-        <v>39.04320811170213</v>
+        <v>34.12143521388717</v>
       </c>
     </row>
     <row r="30">
@@ -2657,13 +2657,13 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D30" t="n">
-        <v>18.07</v>
+        <v>19.34</v>
       </c>
       <c r="E30" t="n">
-        <v>1084.2</v>
+        <v>1160.4</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
@@ -2711,13 +2711,13 @@
         <v>2</v>
       </c>
       <c r="U30" t="n">
-        <v>19.5494964028777</v>
+        <v>18.26573940020682</v>
       </c>
       <c r="V30" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W30" t="n">
-        <v>47.13840619811843</v>
+        <v>44.61427094105481</v>
       </c>
     </row>
     <row r="31">
@@ -2732,25 +2732,25 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D31" t="n">
-        <v>34.68</v>
+        <v>35.53</v>
       </c>
       <c r="E31" t="n">
-        <v>2080.8</v>
+        <v>2131.8</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H31" t="n">
         <v>8</v>
       </c>
       <c r="I31" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J31" t="n">
         <v>5</v>
@@ -2762,7 +2762,7 @@
         <v>2</v>
       </c>
       <c r="M31" t="n">
-        <v>0.4375</v>
+        <v>0.42</v>
       </c>
       <c r="N31" t="n">
         <v>0</v>
@@ -2786,13 +2786,13 @@
         <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>43.0395184544406</v>
+        <v>43.36919504643964</v>
       </c>
       <c r="V31" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="W31" t="n">
-        <v>8.254682814302194</v>
+        <v>9.742609062763865</v>
       </c>
     </row>
     <row r="32">
@@ -2807,13 +2807,13 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D32" t="n">
-        <v>29.53</v>
+        <v>31.71</v>
       </c>
       <c r="E32" t="n">
-        <v>1771.8</v>
+        <v>1902.6</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
@@ -2831,10 +2831,10 @@
         <v>3</v>
       </c>
       <c r="K32" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L32" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M32" t="n">
         <v>0.4642857142857143</v>
@@ -2852,22 +2852,22 @@
         <v>1</v>
       </c>
       <c r="R32" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S32" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T32" t="n">
         <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>32.23455807653234</v>
+        <v>32.62610848312836</v>
       </c>
       <c r="V32" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W32" t="n">
-        <v>4.096769387064005</v>
+        <v>1.492128666035953</v>
       </c>
     </row>
     <row r="33">
@@ -3107,13 +3107,13 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D36" t="n">
-        <v>37.74</v>
+        <v>39.07</v>
       </c>
       <c r="E36" t="n">
-        <v>2264.4</v>
+        <v>2344.2</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
@@ -3146,7 +3146,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q36" t="n">
         <v>1</v>
@@ -3161,13 +3161,13 @@
         <v>8</v>
       </c>
       <c r="U36" t="n">
-        <v>32.3515951245363</v>
+        <v>32.43221909393397</v>
       </c>
       <c r="V36" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="W36" t="n">
-        <v>6.04702702702703</v>
+        <v>2.484348605067829</v>
       </c>
     </row>
     <row r="37">
@@ -3182,13 +3182,13 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D37" t="n">
-        <v>26.99</v>
+        <v>27.91</v>
       </c>
       <c r="E37" t="n">
-        <v>1619.4</v>
+        <v>1674.6</v>
       </c>
       <c r="F37" t="n">
         <v>0</v>
@@ -3236,13 +3236,13 @@
         <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>24.50875138940349</v>
+        <v>23.70086707273379</v>
       </c>
       <c r="V37" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W37" t="n">
-        <v>1.161456094849945</v>
+        <v>-3.716141168040129</v>
       </c>
     </row>
     <row r="38">
@@ -5057,13 +5057,13 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D62" t="n">
-        <v>2.88</v>
+        <v>3.430000000000001</v>
       </c>
       <c r="E62" t="n">
-        <v>172.8</v>
+        <v>205.8</v>
       </c>
       <c r="F62" t="n">
         <v>0</v>
@@ -5111,13 +5111,13 @@
         <v>1</v>
       </c>
       <c r="U62" t="n">
-        <v>32.70763888888888</v>
+        <v>27.46297376093294</v>
       </c>
       <c r="V62" t="n">
         <v>4</v>
       </c>
       <c r="W62" t="n">
-        <v>178.6038888888889</v>
+        <v>149.9647813411079</v>
       </c>
     </row>
     <row r="63">
@@ -5132,22 +5132,22 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D63" t="n">
-        <v>13.11</v>
+        <v>15.99</v>
       </c>
       <c r="E63" t="n">
-        <v>786.6</v>
+        <v>959.4</v>
       </c>
       <c r="F63" t="n">
         <v>0</v>
       </c>
       <c r="G63" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H63" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I63" t="n">
         <v>0</v>
@@ -5171,28 +5171,28 @@
         <v>0</v>
       </c>
       <c r="P63" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q63" t="n">
         <v>0</v>
       </c>
       <c r="R63" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T63" t="n">
         <v>1</v>
       </c>
       <c r="U63" t="n">
-        <v>17.11353165522502</v>
+        <v>24.83792370231395</v>
       </c>
       <c r="V63" t="n">
         <v>6</v>
       </c>
       <c r="W63" t="n">
-        <v>26.95942028985507</v>
+        <v>14.9766353971232</v>
       </c>
     </row>
     <row r="64">
@@ -5357,13 +5357,13 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D66" t="n">
-        <v>48.67</v>
+        <v>52.12</v>
       </c>
       <c r="E66" t="n">
-        <v>2920.2</v>
+        <v>3127.2</v>
       </c>
       <c r="F66" t="n">
         <v>0</v>
@@ -5393,7 +5393,7 @@
         <v>0</v>
       </c>
       <c r="O66" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="P66" t="n">
         <v>5</v>
@@ -5411,13 +5411,13 @@
         <v>5</v>
       </c>
       <c r="U66" t="n">
-        <v>37.59169098006986</v>
+        <v>35.10336914811973</v>
       </c>
       <c r="V66" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="W66" t="n">
-        <v>38.04244709266489</v>
+        <v>34.74717766692249</v>
       </c>
     </row>
     <row r="67">
@@ -5432,22 +5432,22 @@
         </is>
       </c>
       <c r="C67" t="n">
+        <v>9</v>
+      </c>
+      <c r="D67" t="n">
+        <v>21.11</v>
+      </c>
+      <c r="E67" t="n">
+        <v>1266.6</v>
+      </c>
+      <c r="F67" t="n">
+        <v>0</v>
+      </c>
+      <c r="G67" t="n">
         <v>8</v>
       </c>
-      <c r="D67" t="n">
-        <v>18.44</v>
-      </c>
-      <c r="E67" t="n">
-        <v>1106.4</v>
-      </c>
-      <c r="F67" t="n">
-        <v>0</v>
-      </c>
-      <c r="G67" t="n">
-        <v>7</v>
-      </c>
       <c r="H67" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I67" t="n">
         <v>0</v>
@@ -5462,7 +5462,7 @@
         <v>4</v>
       </c>
       <c r="M67" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.75</v>
       </c>
       <c r="N67" t="n">
         <v>0</v>
@@ -5486,13 +5486,13 @@
         <v>3</v>
       </c>
       <c r="U67" t="n">
-        <v>39.66749457700651</v>
+        <v>37.24191852202748</v>
       </c>
       <c r="V67" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="W67" t="n">
-        <v>120.7331073752711</v>
+        <v>111.5983041212695</v>
       </c>
     </row>
     <row r="68">
@@ -5507,13 +5507,13 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D68" t="n">
-        <v>9.4</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="E68" t="n">
-        <v>564</v>
+        <v>597</v>
       </c>
       <c r="F68" t="n">
         <v>0</v>
@@ -5561,13 +5561,13 @@
         <v>1</v>
       </c>
       <c r="U68" t="n">
-        <v>27.89906382978723</v>
+        <v>26.35690452261306</v>
       </c>
       <c r="V68" t="n">
         <v>7</v>
       </c>
       <c r="W68" t="n">
-        <v>35.61634042553191</v>
+        <v>33.64759798994974</v>
       </c>
     </row>
     <row r="69">
@@ -5582,25 +5582,25 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D69" t="n">
-        <v>45.45</v>
+        <v>49.45</v>
       </c>
       <c r="E69" t="n">
-        <v>2727</v>
+        <v>2967</v>
       </c>
       <c r="F69" t="n">
         <v>0</v>
       </c>
       <c r="G69" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H69" t="n">
         <v>5</v>
       </c>
       <c r="I69" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J69" t="n">
         <v>1</v>
@@ -5612,16 +5612,16 @@
         <v>5</v>
       </c>
       <c r="M69" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.3928571428571428</v>
       </c>
       <c r="N69" t="n">
         <v>0</v>
       </c>
       <c r="O69" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P69" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q69" t="n">
         <v>5</v>
@@ -5636,13 +5636,13 @@
         <v>4</v>
       </c>
       <c r="U69" t="n">
-        <v>24.41708910891089</v>
+        <v>25.96879069767442</v>
       </c>
       <c r="V69" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="W69" t="n">
-        <v>29.93966556655665</v>
+        <v>26.75991506572295</v>
       </c>
     </row>
     <row r="70">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D70" t="n">
-        <v>6.07</v>
+        <v>9.52</v>
       </c>
       <c r="E70" t="n">
-        <v>364.2</v>
+        <v>571.2</v>
       </c>
       <c r="F70" t="n">
         <v>0</v>
@@ -5711,13 +5711,13 @@
         <v>1</v>
       </c>
       <c r="U70" t="n">
-        <v>10.25</v>
+        <v>6.53545168067227</v>
       </c>
       <c r="V70" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W70" t="n">
-        <v>6.29</v>
+        <v>-0.2439810924369741</v>
       </c>
     </row>
     <row r="71">
@@ -5807,13 +5807,13 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D72" t="n">
-        <v>56.34</v>
+        <v>58.79</v>
       </c>
       <c r="E72" t="n">
-        <v>3380.4</v>
+        <v>3527.4</v>
       </c>
       <c r="F72" t="n">
         <v>0</v>
@@ -5831,10 +5831,10 @@
         <v>4</v>
       </c>
       <c r="K72" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L72" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M72" t="n">
         <v>0.7368421052631579</v>
@@ -5861,13 +5861,13 @@
         <v>7</v>
       </c>
       <c r="U72" t="n">
-        <v>29.2469595314164</v>
+        <v>28.97328967511482</v>
       </c>
       <c r="V72" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="W72" t="n">
-        <v>35.15067092651758</v>
+        <v>30.90117026705222</v>
       </c>
     </row>
     <row r="73">
@@ -5957,13 +5957,13 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D74" t="n">
-        <v>13.37</v>
+        <v>18.24</v>
       </c>
       <c r="E74" t="n">
-        <v>802.2</v>
+        <v>1094.4</v>
       </c>
       <c r="F74" t="n">
         <v>0</v>
@@ -5981,10 +5981,10 @@
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="L74" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M74" t="n">
         <v>0.3333333333333333</v>
@@ -5996,28 +5996,28 @@
         <v>1</v>
       </c>
       <c r="P74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q74" t="n">
         <v>1</v>
       </c>
       <c r="R74" t="n">
+        <v>7</v>
+      </c>
+      <c r="S74" t="n">
         <v>5</v>
       </c>
-      <c r="S74" t="n">
-        <v>3</v>
-      </c>
       <c r="T74" t="n">
         <v>2</v>
       </c>
       <c r="U74" t="n">
-        <v>33.55863126402393</v>
+        <v>36.16754385964911</v>
       </c>
       <c r="V74" t="n">
-        <v>-17</v>
+        <v>-11</v>
       </c>
       <c r="W74" t="n">
-        <v>-70.97841436050861</v>
+        <v>-29.90423245614035</v>
       </c>
     </row>
     <row r="75">
@@ -6257,19 +6257,19 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D78" t="n">
-        <v>4.779999999999999</v>
+        <v>9.65</v>
       </c>
       <c r="E78" t="n">
-        <v>286.8</v>
+        <v>579</v>
       </c>
       <c r="F78" t="n">
         <v>0</v>
       </c>
       <c r="G78" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H78" t="n">
         <v>1</v>
@@ -6287,7 +6287,7 @@
         <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="N78" t="n">
         <v>0</v>
@@ -6296,28 +6296,28 @@
         <v>0</v>
       </c>
       <c r="P78" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q78" t="n">
         <v>1</v>
       </c>
       <c r="R78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
       </c>
       <c r="T78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U78" t="n">
-        <v>30.0628661087866</v>
+        <v>32.91276683937824</v>
       </c>
       <c r="V78" t="n">
-        <v>-7</v>
+        <v>-1</v>
       </c>
       <c r="W78" t="n">
-        <v>-84.02916317991632</v>
+        <v>0.1936580310880777</v>
       </c>
     </row>
     <row r="79">
@@ -6332,13 +6332,13 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D79" t="n">
-        <v>0.82</v>
+        <v>5.37</v>
       </c>
       <c r="E79" t="n">
-        <v>49.2</v>
+        <v>322.2</v>
       </c>
       <c r="F79" t="n">
         <v>0</v>
@@ -6377,10 +6377,10 @@
         <v>0</v>
       </c>
       <c r="R79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T79" t="n">
         <v>0</v>
@@ -6389,10 +6389,10 @@
         <v>0</v>
       </c>
       <c r="V79" t="n">
-        <v>-2</v>
+        <v>3</v>
       </c>
       <c r="W79" t="n">
-        <v>0</v>
+        <v>73.10502793296089</v>
       </c>
     </row>
     <row r="80">
@@ -6407,13 +6407,13 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D80" t="n">
-        <v>10.57</v>
+        <v>11.94</v>
       </c>
       <c r="E80" t="n">
-        <v>634.2</v>
+        <v>716.4</v>
       </c>
       <c r="F80" t="n">
         <v>0</v>
@@ -6461,13 +6461,13 @@
         <v>0</v>
       </c>
       <c r="U80" t="n">
-        <v>33.03590350047303</v>
+        <v>29.24535175879397</v>
       </c>
       <c r="V80" t="n">
-        <v>-11</v>
+        <v>-13</v>
       </c>
       <c r="W80" t="n">
-        <v>-47.91565752128666</v>
+        <v>-50.0675376884422</v>
       </c>
     </row>
     <row r="81">
@@ -6478,38 +6478,38 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>J. LARREA IBARBURU</t>
+          <t>J. GONZÁLEZ CHÁVEZ</t>
         </is>
       </c>
       <c r="C81" t="n">
         <v>1</v>
       </c>
       <c r="D81" t="n">
-        <v>1.3</v>
+        <v>3.37</v>
       </c>
       <c r="E81" t="n">
-        <v>78</v>
+        <v>202.2</v>
       </c>
       <c r="F81" t="n">
         <v>0</v>
       </c>
       <c r="G81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H81" t="n">
         <v>0</v>
       </c>
       <c r="I81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M81" t="n">
         <v>0</v>
@@ -6518,31 +6518,31 @@
         <v>0</v>
       </c>
       <c r="O81" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q81" t="n">
         <v>0</v>
       </c>
       <c r="R81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
       </c>
       <c r="T81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U81" t="n">
-        <v>30.56</v>
+        <v>35.46</v>
       </c>
       <c r="V81" t="n">
-        <v>-5</v>
+        <v>10</v>
       </c>
       <c r="W81" t="n">
-        <v>-203.37</v>
+        <v>177.3</v>
       </c>
     </row>
     <row r="82">
@@ -6553,50 +6553,50 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>K. SKUTYELNIK</t>
+          <t>J. LARREA IBARBURU</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D82" t="n">
-        <v>18.14</v>
+        <v>1.3</v>
       </c>
       <c r="E82" t="n">
-        <v>1088.4</v>
+        <v>78</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
       </c>
       <c r="G82" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I82" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K82" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M82" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="N82" t="n">
         <v>0</v>
       </c>
       <c r="O82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P82" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q82" t="n">
         <v>0</v>
@@ -6611,13 +6611,13 @@
         <v>0</v>
       </c>
       <c r="U82" t="n">
-        <v>35.31287761852259</v>
+        <v>30.56</v>
       </c>
       <c r="V82" t="n">
-        <v>-20</v>
+        <v>-5</v>
       </c>
       <c r="W82" t="n">
-        <v>-67.4974421168688</v>
+        <v>-203.37</v>
       </c>
     </row>
     <row r="83">
@@ -6628,71 +6628,71 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>O. BALSELLS PLAZA</t>
+          <t>K. SKUTYELNIK</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D83" t="n">
-        <v>22.79</v>
+        <v>18.32</v>
       </c>
       <c r="E83" t="n">
-        <v>1367.4</v>
+        <v>1099.2</v>
       </c>
       <c r="F83" t="n">
         <v>0</v>
       </c>
       <c r="G83" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H83" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I83" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J83" t="n">
         <v>1</v>
       </c>
       <c r="K83" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L83" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M83" t="n">
-        <v>0.375</v>
+        <v>0.5</v>
       </c>
       <c r="N83" t="n">
         <v>0</v>
       </c>
       <c r="O83" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P83" t="n">
         <v>4</v>
       </c>
       <c r="Q83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R83" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S83" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T83" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U83" t="n">
-        <v>30.30652040368583</v>
+        <v>35.94844978165938</v>
       </c>
       <c r="V83" t="n">
-        <v>-27</v>
+        <v>-20</v>
       </c>
       <c r="W83" t="n">
-        <v>-63.88382623957875</v>
+        <v>-66.56632096069869</v>
       </c>
     </row>
     <row r="84">
@@ -6703,146 +6703,146 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>S. GUEYE</t>
+          <t>O. BALSELLS PLAZA</t>
         </is>
       </c>
       <c r="C84" t="n">
+        <v>8</v>
+      </c>
+      <c r="D84" t="n">
+        <v>27.61</v>
+      </c>
+      <c r="E84" t="n">
+        <v>1656.6</v>
+      </c>
+      <c r="F84" t="n">
+        <v>0</v>
+      </c>
+      <c r="G84" t="n">
+        <v>6</v>
+      </c>
+      <c r="H84" t="n">
+        <v>3</v>
+      </c>
+      <c r="I84" t="n">
         <v>5</v>
       </c>
-      <c r="D84" t="n">
-        <v>16.66</v>
-      </c>
-      <c r="E84" t="n">
-        <v>999.6</v>
-      </c>
-      <c r="F84" t="n">
-        <v>0</v>
-      </c>
-      <c r="G84" t="n">
+      <c r="J84" t="n">
+        <v>3</v>
+      </c>
+      <c r="K84" t="n">
+        <v>7</v>
+      </c>
+      <c r="L84" t="n">
+        <v>5</v>
+      </c>
+      <c r="M84" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="N84" t="n">
+        <v>0</v>
+      </c>
+      <c r="O84" t="n">
+        <v>3</v>
+      </c>
+      <c r="P84" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>1</v>
+      </c>
+      <c r="R84" t="n">
         <v>8</v>
       </c>
-      <c r="H84" t="n">
-        <v>1</v>
-      </c>
-      <c r="I84" t="n">
-        <v>7</v>
-      </c>
-      <c r="J84" t="n">
-        <v>1</v>
-      </c>
-      <c r="K84" t="n">
-        <v>0</v>
-      </c>
-      <c r="L84" t="n">
-        <v>0</v>
-      </c>
-      <c r="M84" t="n">
-        <v>0.1875</v>
-      </c>
-      <c r="N84" t="n">
-        <v>0</v>
-      </c>
-      <c r="O84" t="n">
-        <v>0</v>
-      </c>
-      <c r="P84" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
-      <c r="R84" t="n">
-        <v>4</v>
-      </c>
       <c r="S84" t="n">
         <v>2</v>
       </c>
       <c r="T84" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="U84" t="n">
-        <v>25.37163265306122</v>
+        <v>29.65945671858023</v>
       </c>
       <c r="V84" t="n">
-        <v>-18</v>
+        <v>-23</v>
       </c>
       <c r="W84" t="n">
-        <v>-101.966212484994</v>
+        <v>-39.99090184715683</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>EB FELIPE ANTÓN</t>
+          <t>CB ARIDANE</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>A. SISTAC RODRIGUEZ</t>
+          <t>S. GUEYE</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D85" t="n">
-        <v>39.86</v>
+        <v>16.98</v>
       </c>
       <c r="E85" t="n">
-        <v>2391.6</v>
+        <v>1018.8</v>
       </c>
       <c r="F85" t="n">
         <v>0</v>
       </c>
       <c r="G85" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H85" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I85" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K85" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L85" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>0.4</v>
+        <v>0.1875</v>
       </c>
       <c r="N85" t="n">
         <v>0</v>
       </c>
       <c r="O85" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P85" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q85" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R85" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S85" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T85" t="n">
         <v>2</v>
       </c>
       <c r="U85" t="n">
-        <v>21.83081535373808</v>
+        <v>24.89348645465253</v>
       </c>
       <c r="V85" t="n">
-        <v>36</v>
+        <v>-17</v>
       </c>
       <c r="W85" t="n">
-        <v>34.34524836929251</v>
+        <v>-100.0445877502945</v>
       </c>
     </row>
     <row r="86">
@@ -6853,71 +6853,71 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>B. FERNANDEZ SHEPHARD</t>
+          <t>A. SISTAC RODRIGUEZ</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D86" t="n">
-        <v>21.28</v>
+        <v>42.01</v>
       </c>
       <c r="E86" t="n">
-        <v>1276.8</v>
+        <v>2520.6</v>
       </c>
       <c r="F86" t="n">
         <v>0</v>
       </c>
       <c r="G86" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H86" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I86" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
       </c>
       <c r="K86" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L86" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M86" t="n">
-        <v>0.25</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="N86" t="n">
         <v>0</v>
       </c>
       <c r="O86" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P86" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q86" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R86" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S86" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T86" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U86" t="n">
-        <v>20.03228383458647</v>
+        <v>23.27246607950488</v>
       </c>
       <c r="V86" t="n">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="W86" t="n">
-        <v>-26.72508928571428</v>
+        <v>36.63469650083313</v>
       </c>
     </row>
     <row r="87">
@@ -6928,53 +6928,53 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>E. DUQUE NEGRÍN</t>
+          <t>B. FERNANDEZ SHEPHARD</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D87" t="n">
-        <v>46.12</v>
+        <v>21.93</v>
       </c>
       <c r="E87" t="n">
-        <v>2767.2</v>
+        <v>1315.8</v>
       </c>
       <c r="F87" t="n">
         <v>0</v>
       </c>
       <c r="G87" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="H87" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I87" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K87" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="L87" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="M87" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.25</v>
       </c>
       <c r="N87" t="n">
         <v>0</v>
       </c>
       <c r="O87" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P87" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Q87" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R87" t="n">
         <v>5</v>
@@ -6986,13 +6986,13 @@
         <v>3</v>
       </c>
       <c r="U87" t="n">
-        <v>33.15648525585429</v>
+        <v>19.43853169174647</v>
       </c>
       <c r="V87" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="W87" t="n">
-        <v>7.901628360797916</v>
+        <v>-21.5815503875969</v>
       </c>
     </row>
     <row r="88">
@@ -7003,71 +7003,71 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>F. QUERO CARMONA</t>
+          <t>E. DUQUE NEGRÍN</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="D88" t="n">
-        <v>3.2</v>
+        <v>46.12</v>
       </c>
       <c r="E88" t="n">
-        <v>192</v>
+        <v>2767.2</v>
       </c>
       <c r="F88" t="n">
         <v>0</v>
       </c>
       <c r="G88" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="H88" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I88" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K88" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M88" t="n">
-        <v>0</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="N88" t="n">
         <v>0</v>
       </c>
       <c r="O88" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P88" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q88" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R88" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S88" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T88" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U88" t="n">
-        <v>21.3</v>
+        <v>33.15648525585429</v>
       </c>
       <c r="V88" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="W88" t="n">
-        <v>105.91</v>
+        <v>7.901628360797916</v>
       </c>
     </row>
     <row r="89">
@@ -7078,71 +7078,71 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>J. GALLETTO LAMELA</t>
+          <t>F. QUERO CARMONA</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D89" t="n">
-        <v>32.4</v>
+        <v>3.2</v>
       </c>
       <c r="E89" t="n">
-        <v>1944</v>
+        <v>192</v>
       </c>
       <c r="F89" t="n">
         <v>0</v>
       </c>
       <c r="G89" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="H89" t="n">
+        <v>0</v>
+      </c>
+      <c r="I89" t="n">
+        <v>1</v>
+      </c>
+      <c r="J89" t="n">
+        <v>0</v>
+      </c>
+      <c r="K89" t="n">
+        <v>1</v>
+      </c>
+      <c r="L89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P89" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>0</v>
+      </c>
+      <c r="R89" t="n">
+        <v>0</v>
+      </c>
+      <c r="S89" t="n">
+        <v>0</v>
+      </c>
+      <c r="T89" t="n">
+        <v>0</v>
+      </c>
+      <c r="U89" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="V89" t="n">
         <v>8</v>
       </c>
-      <c r="I89" t="n">
-        <v>6</v>
-      </c>
-      <c r="J89" t="n">
-        <v>1</v>
-      </c>
-      <c r="K89" t="n">
-        <v>17</v>
-      </c>
-      <c r="L89" t="n">
-        <v>14</v>
-      </c>
-      <c r="M89" t="n">
-        <v>0.4473684210526316</v>
-      </c>
-      <c r="N89" t="n">
-        <v>0</v>
-      </c>
-      <c r="O89" t="n">
-        <v>5</v>
-      </c>
-      <c r="P89" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q89" t="n">
-        <v>2</v>
-      </c>
-      <c r="R89" t="n">
-        <v>7</v>
-      </c>
-      <c r="S89" t="n">
-        <v>3</v>
-      </c>
-      <c r="T89" t="n">
-        <v>4</v>
-      </c>
-      <c r="U89" t="n">
-        <v>43.25430864197531</v>
-      </c>
-      <c r="V89" t="n">
-        <v>35</v>
-      </c>
       <c r="W89" t="n">
-        <v>50.89822222222223</v>
+        <v>105.91</v>
       </c>
     </row>
     <row r="90">
@@ -7153,71 +7153,71 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>K. RIVEROL DE LAS CASAS</t>
+          <t>J. GALLETTO LAMELA</t>
         </is>
       </c>
       <c r="C90" t="n">
         <v>12</v>
       </c>
       <c r="D90" t="n">
-        <v>31.77</v>
+        <v>34.58</v>
       </c>
       <c r="E90" t="n">
-        <v>1906.2</v>
+        <v>2074.8</v>
       </c>
       <c r="F90" t="n">
         <v>0</v>
       </c>
       <c r="G90" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="H90" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="I90" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J90" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K90" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="L90" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="M90" t="n">
-        <v>0.5</v>
+        <v>0.4523809523809524</v>
       </c>
       <c r="N90" t="n">
         <v>0</v>
       </c>
       <c r="O90" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="P90" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Q90" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R90" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="S90" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T90" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U90" t="n">
-        <v>19.32962543279824</v>
+        <v>43.04914979757084</v>
       </c>
       <c r="V90" t="n">
-        <v>-6</v>
+        <v>37</v>
       </c>
       <c r="W90" t="n">
-        <v>1.195536669814292</v>
+        <v>49.81968189705032</v>
       </c>
     </row>
     <row r="91">
@@ -7228,38 +7228,38 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>L. GIFREU LLARCH</t>
+          <t>K. RIVEROL DE LAS CASAS</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="D91" t="n">
-        <v>23.48</v>
+        <v>33.95</v>
       </c>
       <c r="E91" t="n">
-        <v>1408.8</v>
+        <v>2037</v>
       </c>
       <c r="F91" t="n">
         <v>0</v>
       </c>
       <c r="G91" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H91" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I91" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K91" t="n">
+        <v>13</v>
+      </c>
+      <c r="L91" t="n">
         <v>10</v>
-      </c>
-      <c r="L91" t="n">
-        <v>6</v>
       </c>
       <c r="M91" t="n">
         <v>0.5</v>
@@ -7268,31 +7268,31 @@
         <v>0</v>
       </c>
       <c r="O91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P91" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q91" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R91" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S91" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T91" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U91" t="n">
-        <v>24.80367120954003</v>
+        <v>18.08843004418262</v>
       </c>
       <c r="V91" t="n">
-        <v>5</v>
+        <v>-4</v>
       </c>
       <c r="W91" t="n">
-        <v>21.80133730834753</v>
+        <v>3.288494845360826</v>
       </c>
     </row>
     <row r="92">
@@ -7303,41 +7303,41 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>M. KHIVRENKO</t>
+          <t>L. GIFREU LLARCH</t>
         </is>
       </c>
       <c r="C92" t="n">
+        <v>4</v>
+      </c>
+      <c r="D92" t="n">
+        <v>23.48</v>
+      </c>
+      <c r="E92" t="n">
+        <v>1408.8</v>
+      </c>
+      <c r="F92" t="n">
+        <v>0</v>
+      </c>
+      <c r="G92" t="n">
         <v>5</v>
       </c>
-      <c r="D92" t="n">
-        <v>10.33</v>
-      </c>
-      <c r="E92" t="n">
-        <v>619.8</v>
-      </c>
-      <c r="F92" t="n">
-        <v>0</v>
-      </c>
-      <c r="G92" t="n">
-        <v>0</v>
-      </c>
       <c r="H92" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I92" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K92" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="L92" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M92" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="N92" t="n">
         <v>0</v>
@@ -7346,28 +7346,28 @@
         <v>0</v>
       </c>
       <c r="P92" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q92" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R92" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S92" t="n">
         <v>3</v>
       </c>
       <c r="T92" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U92" t="n">
-        <v>12.28386253630203</v>
+        <v>24.80367120954003</v>
       </c>
       <c r="V92" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W92" t="n">
-        <v>21.89678606001936</v>
+        <v>21.80133730834753</v>
       </c>
     </row>
     <row r="93">
@@ -7378,26 +7378,26 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>M. NIMAGA</t>
+          <t>M. KHIVRENKO</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D93" t="n">
-        <v>35.4</v>
+        <v>10.33</v>
       </c>
       <c r="E93" t="n">
-        <v>2124</v>
+        <v>619.8</v>
       </c>
       <c r="F93" t="n">
         <v>0</v>
       </c>
       <c r="G93" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="H93" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I93" t="n">
         <v>0</v>
@@ -7406,43 +7406,43 @@
         <v>0</v>
       </c>
       <c r="K93" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="L93" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M93" t="n">
-        <v>0.4545454545454545</v>
+        <v>0</v>
       </c>
       <c r="N93" t="n">
         <v>0</v>
       </c>
       <c r="O93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P93" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R93" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="S93" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="T93" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="U93" t="n">
-        <v>30.44561299435028</v>
+        <v>12.28386253630203</v>
       </c>
       <c r="V93" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="W93" t="n">
-        <v>35.25031073446327</v>
+        <v>21.89678606001936</v>
       </c>
     </row>
     <row r="94">
@@ -7453,41 +7453,41 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>P. ARGÜELLES ELORZA</t>
+          <t>M. NIMAGA</t>
         </is>
       </c>
       <c r="C94" t="n">
         <v>10</v>
       </c>
       <c r="D94" t="n">
-        <v>34.89</v>
+        <v>36.93</v>
       </c>
       <c r="E94" t="n">
-        <v>2093.4</v>
+        <v>2215.8</v>
       </c>
       <c r="F94" t="n">
         <v>0</v>
       </c>
       <c r="G94" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="H94" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I94" t="n">
+        <v>0</v>
+      </c>
+      <c r="J94" t="n">
+        <v>0</v>
+      </c>
+      <c r="K94" t="n">
+        <v>11</v>
+      </c>
+      <c r="L94" t="n">
         <v>5</v>
       </c>
-      <c r="J94" t="n">
-        <v>1</v>
-      </c>
-      <c r="K94" t="n">
-        <v>0</v>
-      </c>
-      <c r="L94" t="n">
-        <v>0</v>
-      </c>
       <c r="M94" t="n">
-        <v>0.3571428571428572</v>
+        <v>0.5</v>
       </c>
       <c r="N94" t="n">
         <v>0</v>
@@ -7496,28 +7496,28 @@
         <v>1</v>
       </c>
       <c r="P94" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q94" t="n">
         <v>1</v>
       </c>
       <c r="R94" t="n">
+        <v>22</v>
+      </c>
+      <c r="S94" t="n">
+        <v>12</v>
+      </c>
+      <c r="T94" t="n">
         <v>10</v>
       </c>
-      <c r="S94" t="n">
-        <v>3</v>
-      </c>
-      <c r="T94" t="n">
-        <v>7</v>
-      </c>
       <c r="U94" t="n">
-        <v>15.08938664373746</v>
+        <v>30.22000270782561</v>
       </c>
       <c r="V94" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="W94" t="n">
-        <v>28.48952135282317</v>
+        <v>33.4294611427024</v>
       </c>
     </row>
     <row r="95">
@@ -7528,32 +7528,32 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>P. HERNANDEZ RODRIGUEZ</t>
+          <t>P. ARGÜELLES ELORZA</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D95" t="n">
-        <v>4.17</v>
+        <v>34.92</v>
       </c>
       <c r="E95" t="n">
-        <v>250.2</v>
+        <v>2095.2</v>
       </c>
       <c r="F95" t="n">
         <v>0</v>
       </c>
       <c r="G95" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H95" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I95" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K95" t="n">
         <v>0</v>
@@ -7562,7 +7562,7 @@
         <v>0</v>
       </c>
       <c r="M95" t="n">
-        <v>0</v>
+        <v>0.3571428571428572</v>
       </c>
       <c r="N95" t="n">
         <v>0</v>
@@ -7571,28 +7571,28 @@
         <v>1</v>
       </c>
       <c r="P95" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R95" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="S95" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T95" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="U95" t="n">
-        <v>11.07098321342926</v>
+        <v>15.07642325315006</v>
       </c>
       <c r="V95" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="W95" t="n">
-        <v>65.99067146282975</v>
+        <v>28.4650458190149</v>
       </c>
     </row>
     <row r="96">
@@ -7603,146 +7603,146 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>S. MANERO GUZMAN</t>
+          <t>P. HERNANDEZ RODRIGUEZ</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D96" t="n">
-        <v>46.15</v>
+        <v>4.17</v>
       </c>
       <c r="E96" t="n">
-        <v>2769</v>
+        <v>250.2</v>
       </c>
       <c r="F96" t="n">
         <v>0</v>
       </c>
       <c r="G96" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="H96" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="I96" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J96" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K96" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L96" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M96" t="n">
-        <v>0.8666666666666667</v>
+        <v>0</v>
       </c>
       <c r="N96" t="n">
         <v>0</v>
       </c>
       <c r="O96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R96" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="S96" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T96" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U96" t="n">
-        <v>20.42591982665222</v>
+        <v>11.07098321342926</v>
       </c>
       <c r="V96" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="W96" t="n">
-        <v>41.46951245937161</v>
+        <v>65.99067146282975</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>GRUPO EGIDO PINTOBASKET</t>
+          <t>EB FELIPE ANTÓN</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>C. BARROS CONDES</t>
+          <t>S. MANERO GUZMAN</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D97" t="n">
-        <v>40.81</v>
+        <v>48.33</v>
       </c>
       <c r="E97" t="n">
-        <v>2448.6</v>
+        <v>2899.8</v>
       </c>
       <c r="F97" t="n">
         <v>0</v>
       </c>
       <c r="G97" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H97" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="I97" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="J97" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K97" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="L97" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="M97" t="n">
-        <v>0.5294117647058824</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="N97" t="n">
         <v>0</v>
       </c>
       <c r="O97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P97" t="n">
         <v>1</v>
       </c>
       <c r="Q97" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R97" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S97" t="n">
         <v>2</v>
       </c>
       <c r="T97" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U97" t="n">
-        <v>28.65992403822592</v>
+        <v>19.50457686737016</v>
       </c>
       <c r="V97" t="n">
-        <v>-12</v>
+        <v>26</v>
       </c>
       <c r="W97" t="n">
-        <v>-15.93933104631217</v>
+        <v>41.12311607697082</v>
       </c>
     </row>
     <row r="98">
@@ -7753,71 +7753,71 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>D. TOLOSA OROPESA</t>
+          <t>C. BARROS CONDES</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D98" t="n">
-        <v>33.9</v>
+        <v>40.81</v>
       </c>
       <c r="E98" t="n">
-        <v>2034</v>
+        <v>2448.6</v>
       </c>
       <c r="F98" t="n">
         <v>0</v>
       </c>
       <c r="G98" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H98" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I98" t="n">
+        <v>16</v>
+      </c>
+      <c r="J98" t="n">
         <v>6</v>
       </c>
-      <c r="J98" t="n">
-        <v>1</v>
-      </c>
       <c r="K98" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="L98" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="M98" t="n">
-        <v>0.3214285714285715</v>
+        <v>0.5294117647058824</v>
       </c>
       <c r="N98" t="n">
         <v>0</v>
       </c>
       <c r="O98" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P98" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q98" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R98" t="n">
         <v>5</v>
       </c>
       <c r="S98" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T98" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U98" t="n">
-        <v>29.60564601769912</v>
+        <v>28.65992403822592</v>
       </c>
       <c r="V98" t="n">
-        <v>-5</v>
+        <v>-12</v>
       </c>
       <c r="W98" t="n">
-        <v>-15.86412979351032</v>
+        <v>-15.93933104631217</v>
       </c>
     </row>
     <row r="99">
@@ -7828,71 +7828,71 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>F. SANTAMARIA LEON</t>
+          <t>D. TOLOSA OROPESA</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D99" t="n">
-        <v>6.02</v>
+        <v>33.9</v>
       </c>
       <c r="E99" t="n">
-        <v>361.2</v>
+        <v>2034</v>
       </c>
       <c r="F99" t="n">
         <v>0</v>
       </c>
       <c r="G99" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="H99" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I99" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K99" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M99" t="n">
-        <v>1</v>
+        <v>0.3214285714285715</v>
       </c>
       <c r="N99" t="n">
         <v>0</v>
       </c>
       <c r="O99" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P99" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q99" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R99" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S99" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T99" t="n">
         <v>1</v>
       </c>
       <c r="U99" t="n">
-        <v>6.212624584717608</v>
+        <v>29.60564601769912</v>
       </c>
       <c r="V99" t="n">
-        <v>-13</v>
+        <v>-5</v>
       </c>
       <c r="W99" t="n">
-        <v>-97.53496677740864</v>
+        <v>-15.86412979351032</v>
       </c>
     </row>
     <row r="100">
@@ -7903,71 +7903,71 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>J. AYALA AYLLÓN</t>
+          <t>F. SANTAMARIA LEON</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D100" t="n">
-        <v>43.56</v>
+        <v>6.02</v>
       </c>
       <c r="E100" t="n">
-        <v>2613.6</v>
+        <v>361.2</v>
       </c>
       <c r="F100" t="n">
         <v>0</v>
       </c>
       <c r="G100" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="H100" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I100" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K100" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L100" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M100" t="n">
-        <v>0.2916666666666667</v>
+        <v>1</v>
       </c>
       <c r="N100" t="n">
         <v>0</v>
       </c>
       <c r="O100" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P100" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Q100" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R100" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="S100" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T100" t="n">
         <v>1</v>
       </c>
       <c r="U100" t="n">
-        <v>33.74996556473828</v>
+        <v>6.212624584717608</v>
       </c>
       <c r="V100" t="n">
-        <v>-11</v>
+        <v>-13</v>
       </c>
       <c r="W100" t="n">
-        <v>-18.17979109274564</v>
+        <v>-97.53496677740864</v>
       </c>
     </row>
     <row r="101">
@@ -7978,71 +7978,71 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>J. SAEZ BENITO</t>
+          <t>J. AYALA AYLLÓN</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="D101" t="n">
-        <v>7.49</v>
+        <v>48.36</v>
       </c>
       <c r="E101" t="n">
-        <v>449.4</v>
+        <v>2901.6</v>
       </c>
       <c r="F101" t="n">
         <v>0</v>
       </c>
       <c r="G101" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="H101" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I101" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K101" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L101" t="n">
+        <v>3</v>
+      </c>
+      <c r="M101" t="n">
+        <v>0.2692307692307692</v>
+      </c>
+      <c r="N101" t="n">
+        <v>0</v>
+      </c>
+      <c r="O101" t="n">
+        <v>4</v>
+      </c>
+      <c r="P101" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q101" t="n">
+        <v>3</v>
+      </c>
+      <c r="R101" t="n">
+        <v>8</v>
+      </c>
+      <c r="S101" t="n">
         <v>5</v>
       </c>
-      <c r="M101" t="n">
-        <v>0</v>
-      </c>
-      <c r="N101" t="n">
-        <v>0</v>
-      </c>
-      <c r="O101" t="n">
-        <v>0</v>
-      </c>
-      <c r="P101" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q101" t="n">
-        <v>1</v>
-      </c>
-      <c r="R101" t="n">
-        <v>2</v>
-      </c>
-      <c r="S101" t="n">
-        <v>2</v>
-      </c>
       <c r="T101" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U101" t="n">
-        <v>20.0852870493992</v>
+        <v>33.70828163771711</v>
       </c>
       <c r="V101" t="n">
-        <v>-5</v>
+        <v>-12</v>
       </c>
       <c r="W101" t="n">
-        <v>-48.38883845126836</v>
+        <v>-18.9738564929694</v>
       </c>
     </row>
     <row r="102">
@@ -8053,17 +8053,17 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>J. TRUJILLO FERNÁNDEZ</t>
+          <t>J. SAEZ BENITO</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D102" t="n">
-        <v>3.45</v>
+        <v>11.22</v>
       </c>
       <c r="E102" t="n">
-        <v>207</v>
+        <v>673.2</v>
       </c>
       <c r="F102" t="n">
         <v>0</v>
@@ -8081,10 +8081,10 @@
         <v>0</v>
       </c>
       <c r="K102" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L102" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M102" t="n">
         <v>0</v>
@@ -8093,31 +8093,31 @@
         <v>0</v>
       </c>
       <c r="O102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q102" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R102" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S102" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T102" t="n">
         <v>0</v>
       </c>
       <c r="U102" t="n">
-        <v>14.49275362318841</v>
+        <v>17.81295008912656</v>
       </c>
       <c r="V102" t="n">
-        <v>-2</v>
+        <v>-6</v>
       </c>
       <c r="W102" t="n">
-        <v>-4.850376811594202</v>
+        <v>-46.00561497326203</v>
       </c>
     </row>
     <row r="103">
@@ -8128,71 +8128,71 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>L. BERMEJO ALCALDE</t>
+          <t>J. TRUJILLO FERNÁNDEZ</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D103" t="n">
-        <v>31.04</v>
+        <v>3.45</v>
       </c>
       <c r="E103" t="n">
-        <v>1862.4</v>
+        <v>207</v>
       </c>
       <c r="F103" t="n">
         <v>0</v>
       </c>
       <c r="G103" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H103" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I103" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
       </c>
       <c r="K103" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L103" t="n">
         <v>0</v>
       </c>
       <c r="M103" t="n">
-        <v>0.1666666666666667</v>
+        <v>0</v>
       </c>
       <c r="N103" t="n">
         <v>0</v>
       </c>
       <c r="O103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P103" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q103" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R103" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="S103" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T103" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="U103" t="n">
-        <v>26.34727770618557</v>
+        <v>14.49275362318841</v>
       </c>
       <c r="V103" t="n">
-        <v>-13</v>
+        <v>-2</v>
       </c>
       <c r="W103" t="n">
-        <v>-35.9585212628866</v>
+        <v>-4.850376811594202</v>
       </c>
     </row>
     <row r="104">
@@ -8203,71 +8203,71 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>M. ALARCON ORTIZ</t>
+          <t>L. BERMEJO ALCALDE</t>
         </is>
       </c>
       <c r="C104" t="n">
         <v>11</v>
       </c>
       <c r="D104" t="n">
-        <v>52.6</v>
+        <v>34.97</v>
       </c>
       <c r="E104" t="n">
-        <v>3156</v>
+        <v>2098.2</v>
       </c>
       <c r="F104" t="n">
         <v>0</v>
       </c>
       <c r="G104" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H104" t="n">
+        <v>2</v>
+      </c>
+      <c r="I104" t="n">
+        <v>4</v>
+      </c>
+      <c r="J104" t="n">
+        <v>0</v>
+      </c>
+      <c r="K104" t="n">
+        <v>2</v>
+      </c>
+      <c r="L104" t="n">
+        <v>0</v>
+      </c>
+      <c r="M104" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="N104" t="n">
+        <v>0</v>
+      </c>
+      <c r="O104" t="n">
+        <v>1</v>
+      </c>
+      <c r="P104" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q104" t="n">
+        <v>3</v>
+      </c>
+      <c r="R104" t="n">
+        <v>7</v>
+      </c>
+      <c r="S104" t="n">
+        <v>2</v>
+      </c>
+      <c r="T104" t="n">
         <v>5</v>
       </c>
-      <c r="I104" t="n">
-        <v>4</v>
-      </c>
-      <c r="J104" t="n">
-        <v>1</v>
-      </c>
-      <c r="K104" t="n">
-        <v>7</v>
-      </c>
-      <c r="L104" t="n">
-        <v>4</v>
-      </c>
-      <c r="M104" t="n">
-        <v>0.34375</v>
-      </c>
-      <c r="N104" t="n">
-        <v>0</v>
-      </c>
-      <c r="O104" t="n">
-        <v>0</v>
-      </c>
-      <c r="P104" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q104" t="n">
-        <v>6</v>
-      </c>
-      <c r="R104" t="n">
-        <v>11</v>
-      </c>
-      <c r="S104" t="n">
-        <v>4</v>
-      </c>
-      <c r="T104" t="n">
-        <v>7</v>
-      </c>
       <c r="U104" t="n">
-        <v>23.86056844106464</v>
+        <v>23.3863168430083</v>
       </c>
       <c r="V104" t="n">
-        <v>-25</v>
+        <v>-14</v>
       </c>
       <c r="W104" t="n">
-        <v>-26.92663688212929</v>
+        <v>-33.00416356877324</v>
       </c>
     </row>
     <row r="105">
@@ -8278,71 +8278,71 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>M. BATLLE BERNARDO</t>
+          <t>M. ALARCON ORTIZ</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D105" t="n">
-        <v>27.37</v>
+        <v>55.38</v>
       </c>
       <c r="E105" t="n">
-        <v>1642.2</v>
+        <v>3322.8</v>
       </c>
       <c r="F105" t="n">
         <v>0</v>
       </c>
       <c r="G105" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="H105" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I105" t="n">
+        <v>4</v>
+      </c>
+      <c r="J105" t="n">
+        <v>1</v>
+      </c>
+      <c r="K105" t="n">
+        <v>7</v>
+      </c>
+      <c r="L105" t="n">
+        <v>4</v>
+      </c>
+      <c r="M105" t="n">
+        <v>0.3823529411764706</v>
+      </c>
+      <c r="N105" t="n">
+        <v>0</v>
+      </c>
+      <c r="O105" t="n">
+        <v>0</v>
+      </c>
+      <c r="P105" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q105" t="n">
         <v>6</v>
       </c>
-      <c r="J105" t="n">
-        <v>1</v>
-      </c>
-      <c r="K105" t="n">
-        <v>6</v>
-      </c>
-      <c r="L105" t="n">
-        <v>4</v>
-      </c>
-      <c r="M105" t="n">
-        <v>0.2777777777777778</v>
-      </c>
-      <c r="N105" t="n">
-        <v>0</v>
-      </c>
-      <c r="O105" t="n">
-        <v>1</v>
-      </c>
-      <c r="P105" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q105" t="n">
-        <v>2</v>
-      </c>
       <c r="R105" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="S105" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T105" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="U105" t="n">
-        <v>20.69587139203507</v>
+        <v>24.71994041170097</v>
       </c>
       <c r="V105" t="n">
-        <v>-17</v>
+        <v>-23</v>
       </c>
       <c r="W105" t="n">
-        <v>-27.00865546218487</v>
+        <v>-23.46812026002167</v>
       </c>
     </row>
     <row r="106">
@@ -8353,71 +8353,71 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>M. DEL VALLE REGALADO</t>
+          <t>M. BATLLE BERNARDO</t>
         </is>
       </c>
       <c r="C106" t="n">
+        <v>10</v>
+      </c>
+      <c r="D106" t="n">
+        <v>32.17</v>
+      </c>
+      <c r="E106" t="n">
+        <v>1930.2</v>
+      </c>
+      <c r="F106" t="n">
+        <v>0</v>
+      </c>
+      <c r="G106" t="n">
+        <v>11</v>
+      </c>
+      <c r="H106" t="n">
+        <v>2</v>
+      </c>
+      <c r="I106" t="n">
         <v>7</v>
       </c>
-      <c r="D106" t="n">
-        <v>16.35</v>
-      </c>
-      <c r="E106" t="n">
-        <v>981</v>
-      </c>
-      <c r="F106" t="n">
-        <v>0</v>
-      </c>
-      <c r="G106" t="n">
-        <v>4</v>
-      </c>
-      <c r="H106" t="n">
-        <v>1</v>
-      </c>
-      <c r="I106" t="n">
-        <v>1</v>
-      </c>
       <c r="J106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K106" t="n">
+        <v>8</v>
+      </c>
+      <c r="L106" t="n">
         <v>6</v>
       </c>
-      <c r="L106" t="n">
-        <v>5</v>
-      </c>
       <c r="M106" t="n">
-        <v>0.25</v>
+        <v>0.2272727272727273</v>
       </c>
       <c r="N106" t="n">
         <v>0</v>
       </c>
       <c r="O106" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q106" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R106" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S106" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T106" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U106" t="n">
-        <v>23.96331498470948</v>
+        <v>22.58097606465651</v>
       </c>
       <c r="V106" t="n">
-        <v>-6</v>
+        <v>-18</v>
       </c>
       <c r="W106" t="n">
-        <v>9.571559633027521</v>
+        <v>-26.88501398818775</v>
       </c>
     </row>
     <row r="107">
@@ -8428,53 +8428,53 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>M. SANZ CÁMARA</t>
+          <t>M. DEL VALLE REGALADO</t>
         </is>
       </c>
       <c r="C107" t="n">
+        <v>8</v>
+      </c>
+      <c r="D107" t="n">
+        <v>17.22</v>
+      </c>
+      <c r="E107" t="n">
+        <v>1033.2</v>
+      </c>
+      <c r="F107" t="n">
+        <v>0</v>
+      </c>
+      <c r="G107" t="n">
+        <v>4</v>
+      </c>
+      <c r="H107" t="n">
+        <v>1</v>
+      </c>
+      <c r="I107" t="n">
+        <v>1</v>
+      </c>
+      <c r="J107" t="n">
+        <v>0</v>
+      </c>
+      <c r="K107" t="n">
         <v>6</v>
       </c>
-      <c r="D107" t="n">
-        <v>15.43</v>
-      </c>
-      <c r="E107" t="n">
-        <v>925.8</v>
-      </c>
-      <c r="F107" t="n">
-        <v>0</v>
-      </c>
-      <c r="G107" t="n">
-        <v>4</v>
-      </c>
-      <c r="H107" t="n">
-        <v>1</v>
-      </c>
-      <c r="I107" t="n">
-        <v>3</v>
-      </c>
-      <c r="J107" t="n">
-        <v>1</v>
-      </c>
-      <c r="K107" t="n">
-        <v>0</v>
-      </c>
       <c r="L107" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M107" t="n">
-        <v>0.375</v>
+        <v>0.25</v>
       </c>
       <c r="N107" t="n">
         <v>0</v>
       </c>
       <c r="O107" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="P107" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q107" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R107" t="n">
         <v>1</v>
@@ -8486,13 +8486,13 @@
         <v>0</v>
       </c>
       <c r="U107" t="n">
-        <v>21.29530136098509</v>
+        <v>24.5067711962834</v>
       </c>
       <c r="V107" t="n">
-        <v>-10</v>
+        <v>-6</v>
       </c>
       <c r="W107" t="n">
-        <v>-17.4401425793908</v>
+        <v>2.491742160278747</v>
       </c>
     </row>
     <row r="108">
@@ -8503,116 +8503,116 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>S. RODRIGUEZ GREGORIO</t>
+          <t>M. SANZ CÁMARA</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D108" t="n">
-        <v>25.55</v>
+        <v>15.43</v>
       </c>
       <c r="E108" t="n">
-        <v>1533</v>
+        <v>925.8</v>
       </c>
       <c r="F108" t="n">
         <v>0</v>
       </c>
       <c r="G108" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H108" t="n">
         <v>1</v>
       </c>
       <c r="I108" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J108" t="n">
         <v>1</v>
       </c>
       <c r="K108" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L108" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M108" t="n">
-        <v>0.3</v>
+        <v>0.375</v>
       </c>
       <c r="N108" t="n">
         <v>0</v>
       </c>
       <c r="O108" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="P108" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q108" t="n">
         <v>2</v>
       </c>
       <c r="R108" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="S108" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T108" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U108" t="n">
-        <v>13.63736203522505</v>
+        <v>21.29530136098509</v>
       </c>
       <c r="V108" t="n">
-        <v>-12</v>
+        <v>-10</v>
       </c>
       <c r="W108" t="n">
-        <v>-19.5872133072407</v>
+        <v>-17.4401425793908</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>LUJISA GUADALAJARA BASKET</t>
+          <t>GRUPO EGIDO PINTOBASKET</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>A. ALMENARA SANABRIAS</t>
+          <t>S. RODRIGUEZ GREGORIO</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D109" t="n">
-        <v>8.85</v>
+        <v>28.63</v>
       </c>
       <c r="E109" t="n">
-        <v>531</v>
+        <v>1717.8</v>
       </c>
       <c r="F109" t="n">
         <v>0</v>
       </c>
       <c r="G109" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H109" t="n">
         <v>1</v>
       </c>
       <c r="I109" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J109" t="n">
         <v>1</v>
       </c>
       <c r="K109" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L109" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M109" t="n">
-        <v>0.375</v>
+        <v>0.25</v>
       </c>
       <c r="N109" t="n">
         <v>0</v>
@@ -8624,25 +8624,25 @@
         <v>0</v>
       </c>
       <c r="Q109" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R109" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="S109" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T109" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U109" t="n">
-        <v>32.32016949152542</v>
+        <v>14.03784142507859</v>
       </c>
       <c r="V109" t="n">
-        <v>1</v>
+        <v>-15</v>
       </c>
       <c r="W109" t="n">
-        <v>-3.767548022598869</v>
+        <v>-26.19611945511701</v>
       </c>
     </row>
     <row r="110">
@@ -8653,71 +8653,71 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>A. ARMSTRONG</t>
+          <t>A. ALMENARA SANABRIAS</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D110" t="n">
-        <v>36.83</v>
+        <v>8.85</v>
       </c>
       <c r="E110" t="n">
-        <v>2209.8</v>
+        <v>531</v>
       </c>
       <c r="F110" t="n">
         <v>0</v>
       </c>
       <c r="G110" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="H110" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I110" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J110" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K110" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L110" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M110" t="n">
-        <v>0.3823529411764706</v>
+        <v>0.375</v>
       </c>
       <c r="N110" t="n">
         <v>0</v>
       </c>
       <c r="O110" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P110" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q110" t="n">
         <v>0</v>
       </c>
       <c r="R110" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T110" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U110" t="n">
-        <v>31.09381482487103</v>
+        <v>32.32016949152542</v>
       </c>
       <c r="V110" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="W110" t="n">
-        <v>-22.67373065435786</v>
+        <v>-3.767548022598869</v>
       </c>
     </row>
     <row r="111">
@@ -8728,71 +8728,71 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>B. OJEDA OCHOA</t>
+          <t>A. ARMSTRONG</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D111" t="n">
-        <v>38.12</v>
+        <v>36.83</v>
       </c>
       <c r="E111" t="n">
-        <v>2287.2</v>
+        <v>2209.8</v>
       </c>
       <c r="F111" t="n">
         <v>0</v>
       </c>
       <c r="G111" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="H111" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I111" t="n">
         <v>10</v>
       </c>
       <c r="J111" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K111" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="L111" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="M111" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.3823529411764706</v>
       </c>
       <c r="N111" t="n">
         <v>0</v>
       </c>
       <c r="O111" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="P111" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q111" t="n">
         <v>0</v>
       </c>
       <c r="R111" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S111" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T111" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U111" t="n">
-        <v>27.14532791185729</v>
+        <v>31.09381482487103</v>
       </c>
       <c r="V111" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="W111" t="n">
-        <v>-7.625362014690455</v>
+        <v>-22.67373065435786</v>
       </c>
     </row>
     <row r="112">
@@ -8803,71 +8803,71 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>D. BUTUNOI</t>
+          <t>B. OJEDA OCHOA</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D112" t="n">
-        <v>0.02</v>
+        <v>38.12</v>
       </c>
       <c r="E112" t="n">
-        <v>1.2</v>
+        <v>2287.2</v>
       </c>
       <c r="F112" t="n">
         <v>0</v>
       </c>
       <c r="G112" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H112" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I112" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J112" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K112" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L112" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M112" t="n">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="N112" t="n">
         <v>0</v>
       </c>
       <c r="O112" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="P112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q112" t="n">
         <v>0</v>
       </c>
       <c r="R112" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S112" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T112" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U112" t="n">
-        <v>0</v>
+        <v>27.14532791185729</v>
       </c>
       <c r="V112" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W112" t="n">
-        <v>0</v>
+        <v>-7.625362014690455</v>
       </c>
     </row>
     <row r="113">
@@ -8878,71 +8878,71 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>D. EBOLO OLU-ELIJAH</t>
+          <t>D. BUTUNOI</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D113" t="n">
-        <v>35.3</v>
+        <v>0.02</v>
       </c>
       <c r="E113" t="n">
-        <v>2118</v>
+        <v>1.2</v>
       </c>
       <c r="F113" t="n">
         <v>0</v>
       </c>
       <c r="G113" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H113" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I113" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K113" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L113" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M113" t="n">
-        <v>0.4166666666666667</v>
+        <v>0</v>
       </c>
       <c r="N113" t="n">
         <v>0</v>
       </c>
       <c r="O113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P113" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q113" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R113" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="S113" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T113" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="U113" t="n">
-        <v>25.38862606232295</v>
+        <v>0</v>
       </c>
       <c r="V113" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="W113" t="n">
-        <v>3.090005665722384</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -8953,71 +8953,71 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>E. CALVO SALVE</t>
+          <t>D. EBOLO OLU-ELIJAH</t>
         </is>
       </c>
       <c r="C114" t="n">
+        <v>12</v>
+      </c>
+      <c r="D114" t="n">
+        <v>35.3</v>
+      </c>
+      <c r="E114" t="n">
+        <v>2118</v>
+      </c>
+      <c r="F114" t="n">
+        <v>0</v>
+      </c>
+      <c r="G114" t="n">
         <v>6</v>
       </c>
-      <c r="D114" t="n">
-        <v>11.05</v>
-      </c>
-      <c r="E114" t="n">
-        <v>663</v>
-      </c>
-      <c r="F114" t="n">
-        <v>0</v>
-      </c>
-      <c r="G114" t="n">
-        <v>3</v>
-      </c>
       <c r="H114" t="n">
         <v>2</v>
       </c>
       <c r="I114" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K114" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L114" t="n">
         <v>2</v>
       </c>
       <c r="M114" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="N114" t="n">
         <v>0</v>
       </c>
       <c r="O114" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P114" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="Q114" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R114" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="S114" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T114" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U114" t="n">
-        <v>26.24031674208145</v>
+        <v>25.38862606232295</v>
       </c>
       <c r="V114" t="n">
-        <v>5</v>
+        <v>-10</v>
       </c>
       <c r="W114" t="n">
-        <v>-23.71561990950226</v>
+        <v>3.090005665722384</v>
       </c>
     </row>
     <row r="115">
@@ -9028,17 +9028,17 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>F. DIAZ ZARZUELA</t>
+          <t>E. CALVO SALVE</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D115" t="n">
-        <v>12.03</v>
+        <v>11.05</v>
       </c>
       <c r="E115" t="n">
-        <v>721.8</v>
+        <v>663</v>
       </c>
       <c r="F115" t="n">
         <v>0</v>
@@ -9047,7 +9047,7 @@
         <v>3</v>
       </c>
       <c r="H115" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I115" t="n">
         <v>1</v>
@@ -9056,43 +9056,43 @@
         <v>0</v>
       </c>
       <c r="K115" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L115" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M115" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="N115" t="n">
         <v>0</v>
       </c>
       <c r="O115" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P115" t="n">
         <v>1</v>
       </c>
       <c r="Q115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R115" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="S115" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T115" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U115" t="n">
-        <v>19.27557772236077</v>
+        <v>26.24031674208145</v>
       </c>
       <c r="V115" t="n">
-        <v>-6</v>
+        <v>5</v>
       </c>
       <c r="W115" t="n">
-        <v>-70.62108063175396</v>
+        <v>-23.71561990950226</v>
       </c>
     </row>
     <row r="116">
@@ -9103,71 +9103,71 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>J. BUSTOS NGUEMA</t>
+          <t>F. DIAZ ZARZUELA</t>
         </is>
       </c>
       <c r="C116" t="n">
         <v>4</v>
       </c>
       <c r="D116" t="n">
-        <v>8.83</v>
+        <v>12.03</v>
       </c>
       <c r="E116" t="n">
-        <v>529.8</v>
+        <v>721.8</v>
       </c>
       <c r="F116" t="n">
         <v>0</v>
       </c>
       <c r="G116" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H116" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I116" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K116" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L116" t="n">
         <v>0</v>
       </c>
       <c r="M116" t="n">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="N116" t="n">
         <v>0</v>
       </c>
       <c r="O116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q116" t="n">
         <v>0</v>
       </c>
       <c r="R116" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="S116" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T116" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U116" t="n">
-        <v>35.33835787089468</v>
+        <v>19.27557772236077</v>
       </c>
       <c r="V116" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="W116" t="n">
-        <v>-45.05976217440544</v>
+        <v>-70.62108063175396</v>
       </c>
     </row>
     <row r="117">
@@ -9178,41 +9178,41 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>J. HOYA MARTINEZ</t>
+          <t>J. BUSTOS NGUEMA</t>
         </is>
       </c>
       <c r="C117" t="n">
         <v>4</v>
       </c>
       <c r="D117" t="n">
-        <v>15.5</v>
+        <v>8.83</v>
       </c>
       <c r="E117" t="n">
-        <v>930</v>
+        <v>529.8</v>
       </c>
       <c r="F117" t="n">
         <v>0</v>
       </c>
       <c r="G117" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H117" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I117" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K117" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L117" t="n">
         <v>0</v>
       </c>
       <c r="M117" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="N117" t="n">
         <v>0</v>
@@ -9221,7 +9221,7 @@
         <v>0</v>
       </c>
       <c r="P117" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q117" t="n">
         <v>0</v>
@@ -9236,13 +9236,13 @@
         <v>0</v>
       </c>
       <c r="U117" t="n">
-        <v>14.91265806451613</v>
+        <v>35.33835787089468</v>
       </c>
       <c r="V117" t="n">
-        <v>-8</v>
+        <v>0</v>
       </c>
       <c r="W117" t="n">
-        <v>-19.51603870967742</v>
+        <v>-45.05976217440544</v>
       </c>
     </row>
     <row r="118">
@@ -9253,41 +9253,41 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>L. VALERA VILLEGAS</t>
+          <t>J. HOYA MARTINEZ</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D118" t="n">
-        <v>47.05</v>
+        <v>15.5</v>
       </c>
       <c r="E118" t="n">
-        <v>2823</v>
+        <v>930</v>
       </c>
       <c r="F118" t="n">
         <v>0</v>
       </c>
       <c r="G118" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="H118" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I118" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J118" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K118" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="L118" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M118" t="n">
-        <v>0.625</v>
+        <v>0</v>
       </c>
       <c r="N118" t="n">
         <v>0</v>
@@ -9299,25 +9299,25 @@
         <v>2</v>
       </c>
       <c r="Q118" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R118" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="S118" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T118" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="U118" t="n">
-        <v>26.62724548352816</v>
+        <v>14.91265806451613</v>
       </c>
       <c r="V118" t="n">
-        <v>-4</v>
+        <v>-8</v>
       </c>
       <c r="W118" t="n">
-        <v>-11.63287353878852</v>
+        <v>-19.51603870967742</v>
       </c>
     </row>
     <row r="119">
@@ -9328,41 +9328,41 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>M. DIALLO</t>
+          <t>L. VALERA VILLEGAS</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D119" t="n">
-        <v>34.34</v>
+        <v>47.05</v>
       </c>
       <c r="E119" t="n">
-        <v>2060.4</v>
+        <v>2823</v>
       </c>
       <c r="F119" t="n">
         <v>0</v>
       </c>
       <c r="G119" t="n">
+        <v>16</v>
+      </c>
+      <c r="H119" t="n">
         <v>9</v>
       </c>
-      <c r="H119" t="n">
-        <v>5</v>
-      </c>
       <c r="I119" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J119" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K119" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="L119" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="M119" t="n">
-        <v>0.5555555555555556</v>
+        <v>0.625</v>
       </c>
       <c r="N119" t="n">
         <v>0</v>
@@ -9371,103 +9371,103 @@
         <v>0</v>
       </c>
       <c r="P119" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q119" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R119" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="S119" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T119" t="n">
         <v>6</v>
       </c>
       <c r="U119" t="n">
-        <v>21.22257716948165</v>
+        <v>26.62724548352816</v>
       </c>
       <c r="V119" t="n">
-        <v>2</v>
+        <v>-4</v>
       </c>
       <c r="W119" t="n">
-        <v>-1.711543389633081</v>
+        <v>-11.63287353878852</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>REAL CANOE N.C.</t>
+          <t>LUJISA GUADALAJARA BASKET</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>D. MANZANERO CAMACHO</t>
+          <t>M. DIALLO</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D120" t="n">
-        <v>29.92</v>
+        <v>34.34</v>
       </c>
       <c r="E120" t="n">
-        <v>1795.2</v>
+        <v>2060.4</v>
       </c>
       <c r="F120" t="n">
         <v>0</v>
       </c>
       <c r="G120" t="n">
+        <v>9</v>
+      </c>
+      <c r="H120" t="n">
+        <v>5</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0</v>
+      </c>
+      <c r="K120" t="n">
+        <v>3</v>
+      </c>
+      <c r="L120" t="n">
+        <v>1</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.5555555555555556</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0</v>
+      </c>
+      <c r="P120" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>1</v>
+      </c>
+      <c r="R120" t="n">
+        <v>16</v>
+      </c>
+      <c r="S120" t="n">
         <v>10</v>
       </c>
-      <c r="H120" t="n">
-        <v>4</v>
-      </c>
-      <c r="I120" t="n">
-        <v>5</v>
-      </c>
-      <c r="J120" t="n">
-        <v>2</v>
-      </c>
-      <c r="K120" t="n">
-        <v>4</v>
-      </c>
-      <c r="L120" t="n">
-        <v>3</v>
-      </c>
-      <c r="M120" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="N120" t="n">
-        <v>0</v>
-      </c>
-      <c r="O120" t="n">
-        <v>1</v>
-      </c>
-      <c r="P120" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q120" t="n">
-        <v>3</v>
-      </c>
-      <c r="R120" t="n">
-        <v>5</v>
-      </c>
-      <c r="S120" t="n">
-        <v>3</v>
-      </c>
       <c r="T120" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="U120" t="n">
-        <v>24.68615307486631</v>
+        <v>21.22257716948165</v>
       </c>
       <c r="V120" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="W120" t="n">
-        <v>46.82532419786095</v>
+        <v>-1.711543389633081</v>
       </c>
     </row>
     <row r="121">
@@ -9478,41 +9478,41 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>E. MARTINEZ ALVAREZ</t>
+          <t>D. MANZANERO CAMACHO</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D121" t="n">
-        <v>22.29</v>
+        <v>34.72</v>
       </c>
       <c r="E121" t="n">
-        <v>1337.4</v>
+        <v>2083.2</v>
       </c>
       <c r="F121" t="n">
         <v>0</v>
       </c>
       <c r="G121" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="H121" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I121" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J121" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K121" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L121" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M121" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="N121" t="n">
         <v>0</v>
@@ -9521,28 +9521,28 @@
         <v>1</v>
       </c>
       <c r="P121" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q121" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R121" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="S121" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T121" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U121" t="n">
-        <v>21.97650964558098</v>
+        <v>26.93875864055299</v>
       </c>
       <c r="V121" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="W121" t="n">
-        <v>19.95810677433826</v>
+        <v>43.97113191244239</v>
       </c>
     </row>
     <row r="122">
@@ -9553,41 +9553,41 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>E. PASCUAL COZAR</t>
+          <t>E. MARTINEZ ALVAREZ</t>
         </is>
       </c>
       <c r="C122" t="n">
         <v>6</v>
       </c>
       <c r="D122" t="n">
-        <v>15.76</v>
+        <v>22.29</v>
       </c>
       <c r="E122" t="n">
-        <v>945.6</v>
+        <v>1337.4</v>
       </c>
       <c r="F122" t="n">
         <v>0</v>
       </c>
       <c r="G122" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H122" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I122" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K122" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L122" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M122" t="n">
-        <v>0</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="N122" t="n">
         <v>0</v>
@@ -9596,28 +9596,28 @@
         <v>1</v>
       </c>
       <c r="P122" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q122" t="n">
         <v>0</v>
       </c>
       <c r="R122" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S122" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U122" t="n">
-        <v>26.7719035532995</v>
+        <v>21.97650964558098</v>
       </c>
       <c r="V122" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="W122" t="n">
-        <v>25.68480964467006</v>
+        <v>19.95810677433826</v>
       </c>
     </row>
     <row r="123">
@@ -9628,71 +9628,71 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>J. GARCIA-LARRACHE SEGURA</t>
+          <t>E. PASCUAL COZAR</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D123" t="n">
-        <v>20.21</v>
+        <v>15.76</v>
       </c>
       <c r="E123" t="n">
-        <v>1212.6</v>
+        <v>945.6</v>
       </c>
       <c r="F123" t="n">
         <v>0</v>
       </c>
       <c r="G123" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H123" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I123" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
       </c>
       <c r="K123" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L123" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M123" t="n">
-        <v>0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="N123" t="n">
         <v>0</v>
       </c>
       <c r="O123" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P123" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R123" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="S123" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T123" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U123" t="n">
-        <v>34.51264225630874</v>
+        <v>26.7719035532995</v>
       </c>
       <c r="V123" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="W123" t="n">
-        <v>60.26952498762988</v>
+        <v>25.68480964467006</v>
       </c>
     </row>
     <row r="124">
@@ -9703,23 +9703,23 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>J. LAPASTORA ARACIL</t>
+          <t>J. GARCIA-LARRACHE SEGURA</t>
         </is>
       </c>
       <c r="C124" t="n">
+        <v>5</v>
+      </c>
+      <c r="D124" t="n">
+        <v>23.39</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1403.4</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0</v>
+      </c>
+      <c r="G124" t="n">
         <v>8</v>
-      </c>
-      <c r="D124" t="n">
-        <v>25.35</v>
-      </c>
-      <c r="E124" t="n">
-        <v>1521</v>
-      </c>
-      <c r="F124" t="n">
-        <v>0</v>
-      </c>
-      <c r="G124" t="n">
-        <v>6</v>
       </c>
       <c r="H124" t="n">
         <v>2</v>
@@ -9728,22 +9728,22 @@
         <v>5</v>
       </c>
       <c r="J124" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K124" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L124" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M124" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="N124" t="n">
         <v>0</v>
       </c>
       <c r="O124" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P124" t="n">
         <v>4</v>
@@ -9752,22 +9752,22 @@
         <v>1</v>
       </c>
       <c r="R124" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="S124" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T124" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U124" t="n">
-        <v>24.41256015779093</v>
+        <v>36.11519880290722</v>
       </c>
       <c r="V124" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="W124" t="n">
-        <v>51.39020118343196</v>
+        <v>65.9158230012826</v>
       </c>
     </row>
     <row r="125">
@@ -9778,71 +9778,71 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>J. MARTINEZ SANTOS</t>
+          <t>J. LAPASTORA ARACIL</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D125" t="n">
-        <v>2.27</v>
+        <v>29.28</v>
       </c>
       <c r="E125" t="n">
-        <v>136.2</v>
+        <v>1756.8</v>
       </c>
       <c r="F125" t="n">
         <v>0</v>
       </c>
       <c r="G125" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H125" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I125" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J125" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K125" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L125" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M125" t="n">
-        <v>0</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="N125" t="n">
         <v>0</v>
       </c>
       <c r="O125" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P125" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R125" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="S125" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T125" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U125" t="n">
-        <v>19.85814977973568</v>
+        <v>23.25925546448088</v>
       </c>
       <c r="V125" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="W125" t="n">
-        <v>109.765154185022</v>
+        <v>45.79046106557377</v>
       </c>
     </row>
     <row r="126">
@@ -9853,23 +9853,23 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>J. OLIVA SANCHEZ</t>
+          <t>J. MARTINEZ SANTOS</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D126" t="n">
-        <v>0.48</v>
+        <v>2.27</v>
       </c>
       <c r="E126" t="n">
-        <v>28.8</v>
+        <v>136.2</v>
       </c>
       <c r="F126" t="n">
         <v>0</v>
       </c>
       <c r="G126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H126" t="n">
         <v>0</v>
@@ -9893,7 +9893,7 @@
         <v>0</v>
       </c>
       <c r="O126" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P126" t="n">
         <v>0</v>
@@ -9902,22 +9902,22 @@
         <v>0</v>
       </c>
       <c r="R126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T126" t="n">
         <v>0</v>
       </c>
       <c r="U126" t="n">
-        <v>0</v>
+        <v>19.85814977973568</v>
       </c>
       <c r="V126" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W126" t="n">
-        <v>0</v>
+        <v>109.765154185022</v>
       </c>
     </row>
     <row r="127">
@@ -9928,71 +9928,71 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>L. GARCIA LARRACHE SEGURA</t>
+          <t>J. OLIVA SANCHEZ</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D127" t="n">
-        <v>26.01</v>
+        <v>0.48</v>
       </c>
       <c r="E127" t="n">
-        <v>1560.6</v>
+        <v>28.8</v>
       </c>
       <c r="F127" t="n">
         <v>0</v>
       </c>
       <c r="G127" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H127" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I127" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
       </c>
       <c r="K127" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="L127" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="M127" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="N127" t="n">
         <v>0</v>
       </c>
       <c r="O127" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P127" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q127" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R127" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="S127" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T127" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U127" t="n">
-        <v>41.49541714725105</v>
+        <v>0</v>
       </c>
       <c r="V127" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="W127" t="n">
-        <v>56.67328719723184</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128">
@@ -10003,71 +10003,71 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>M. HERMOSO ALCUBILLA</t>
+          <t>L. GARCIA LARRACHE SEGURA</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D128" t="n">
-        <v>21.59</v>
+        <v>30.81</v>
       </c>
       <c r="E128" t="n">
-        <v>1295.4</v>
+        <v>1848.6</v>
       </c>
       <c r="F128" t="n">
         <v>0</v>
       </c>
       <c r="G128" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="H128" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I128" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
       </c>
       <c r="K128" t="n">
+        <v>18</v>
+      </c>
+      <c r="L128" t="n">
         <v>14</v>
       </c>
-      <c r="L128" t="n">
-        <v>10</v>
-      </c>
       <c r="M128" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.75</v>
       </c>
       <c r="N128" t="n">
         <v>0</v>
       </c>
       <c r="O128" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P128" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q128" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R128" t="n">
         <v>6</v>
       </c>
       <c r="S128" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T128" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U128" t="n">
-        <v>31.50892079666513</v>
+        <v>42.09749432002597</v>
       </c>
       <c r="V128" t="n">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="W128" t="n">
-        <v>14.99081982399259</v>
+        <v>51.92262901655307</v>
       </c>
     </row>
     <row r="129">
@@ -10078,71 +10078,71 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>M. KREISLER LORENTE</t>
+          <t>M. HERMOSO ALCUBILLA</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D129" t="n">
-        <v>17.32</v>
+        <v>24.07</v>
       </c>
       <c r="E129" t="n">
-        <v>1039.2</v>
+        <v>1444.2</v>
       </c>
       <c r="F129" t="n">
         <v>0</v>
       </c>
       <c r="G129" t="n">
+        <v>7</v>
+      </c>
+      <c r="H129" t="n">
+        <v>2</v>
+      </c>
+      <c r="I129" t="n">
+        <v>4</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0</v>
+      </c>
+      <c r="K129" t="n">
+        <v>14</v>
+      </c>
+      <c r="L129" t="n">
+        <v>10</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0</v>
+      </c>
+      <c r="P129" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>1</v>
+      </c>
+      <c r="R129" t="n">
         <v>6</v>
       </c>
-      <c r="H129" t="n">
-        <v>2</v>
-      </c>
-      <c r="I129" t="n">
-        <v>5</v>
-      </c>
-      <c r="J129" t="n">
-        <v>1</v>
-      </c>
-      <c r="K129" t="n">
-        <v>6</v>
-      </c>
-      <c r="L129" t="n">
-        <v>4</v>
-      </c>
-      <c r="M129" t="n">
-        <v>0.4166666666666667</v>
-      </c>
-      <c r="N129" t="n">
-        <v>0</v>
-      </c>
-      <c r="O129" t="n">
-        <v>2</v>
-      </c>
-      <c r="P129" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q129" t="n">
-        <v>3</v>
-      </c>
-      <c r="R129" t="n">
-        <v>4</v>
-      </c>
       <c r="S129" t="n">
         <v>3</v>
       </c>
       <c r="T129" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U129" t="n">
-        <v>27.08060046189376</v>
+        <v>30.83828832571666</v>
       </c>
       <c r="V129" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="W129" t="n">
-        <v>45.9400635103926</v>
+        <v>10.1523140839219</v>
       </c>
     </row>
     <row r="130">
@@ -10153,41 +10153,41 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>N. LASUNCION MARIBLANCA</t>
+          <t>M. KREISLER LORENTE</t>
         </is>
       </c>
       <c r="C130" t="n">
+        <v>5</v>
+      </c>
+      <c r="D130" t="n">
+        <v>19.64</v>
+      </c>
+      <c r="E130" t="n">
+        <v>1178.4</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0</v>
+      </c>
+      <c r="G130" t="n">
         <v>7</v>
       </c>
-      <c r="D130" t="n">
-        <v>17.27</v>
-      </c>
-      <c r="E130" t="n">
-        <v>1036.2</v>
-      </c>
-      <c r="F130" t="n">
-        <v>0</v>
-      </c>
-      <c r="G130" t="n">
-        <v>3</v>
-      </c>
       <c r="H130" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I130" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K130" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L130" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M130" t="n">
-        <v>0</v>
+        <v>0.3571428571428572</v>
       </c>
       <c r="N130" t="n">
         <v>0</v>
@@ -10196,28 +10196,28 @@
         <v>2</v>
       </c>
       <c r="P130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q130" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R130" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S130" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T130" t="n">
         <v>1</v>
       </c>
       <c r="U130" t="n">
-        <v>16.03488708743486</v>
+        <v>27.43963340122199</v>
       </c>
       <c r="V130" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="W130" t="n">
-        <v>40.95397220613782</v>
+        <v>52.02001527494908</v>
       </c>
     </row>
     <row r="131">
@@ -10228,38 +10228,38 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>P. FUENTE DIEZ</t>
+          <t>N. LASUNCION MARIBLANCA</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D131" t="n">
-        <v>0.13</v>
+        <v>17.27</v>
       </c>
       <c r="E131" t="n">
-        <v>7.800000000000001</v>
+        <v>1036.2</v>
       </c>
       <c r="F131" t="n">
         <v>0</v>
       </c>
       <c r="G131" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H131" t="n">
         <v>0</v>
       </c>
       <c r="I131" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
       </c>
       <c r="K131" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L131" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M131" t="n">
         <v>0</v>
@@ -10268,7 +10268,7 @@
         <v>0</v>
       </c>
       <c r="O131" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P131" t="n">
         <v>0</v>
@@ -10277,49 +10277,49 @@
         <v>0</v>
       </c>
       <c r="R131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S131" t="n">
         <v>0</v>
       </c>
       <c r="T131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U131" t="n">
-        <v>0</v>
+        <v>16.03488708743486</v>
       </c>
       <c r="V131" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W131" t="n">
-        <v>0</v>
+        <v>40.95397220613782</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>RECUCYM BAZU</t>
+          <t>REAL CANOE N.C.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>D. MARTIN LLUNA</t>
+          <t>P. FUENTE DIEZ</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D132" t="n">
-        <v>3.3</v>
+        <v>2.61</v>
       </c>
       <c r="E132" t="n">
-        <v>198</v>
+        <v>156.6</v>
       </c>
       <c r="F132" t="n">
         <v>0</v>
       </c>
       <c r="G132" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H132" t="n">
         <v>0</v>
@@ -10349,25 +10349,25 @@
         <v>0</v>
       </c>
       <c r="Q132" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R132" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S132" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T132" t="n">
         <v>0</v>
       </c>
       <c r="U132" t="n">
-        <v>9.19</v>
+        <v>0</v>
       </c>
       <c r="V132" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="W132" t="n">
-        <v>-50.04</v>
+        <v>-30.3776245210728</v>
       </c>
     </row>
     <row r="133">
@@ -10378,32 +10378,32 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>E. ECHEVERRIA MATEO</t>
+          <t>D. MARTIN LLUNA</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D133" t="n">
-        <v>21.56</v>
+        <v>3.3</v>
       </c>
       <c r="E133" t="n">
-        <v>1293.6</v>
+        <v>198</v>
       </c>
       <c r="F133" t="n">
         <v>0</v>
       </c>
       <c r="G133" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="H133" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I133" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J133" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K133" t="n">
         <v>0</v>
@@ -10412,37 +10412,37 @@
         <v>0</v>
       </c>
       <c r="M133" t="n">
-        <v>0.2307692307692308</v>
+        <v>0</v>
       </c>
       <c r="N133" t="n">
         <v>0</v>
       </c>
       <c r="O133" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P133" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q133" t="n">
         <v>0</v>
       </c>
       <c r="R133" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="S133" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T133" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U133" t="n">
-        <v>49.39655844155843</v>
+        <v>9.19</v>
       </c>
       <c r="V133" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="W133" t="n">
-        <v>-8.184355287569575</v>
+        <v>-50.04</v>
       </c>
     </row>
     <row r="134">
@@ -10453,71 +10453,71 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>G. HIERRO ABAD</t>
+          <t>E. ECHEVERRIA MATEO</t>
         </is>
       </c>
       <c r="C134" t="n">
         <v>6</v>
       </c>
       <c r="D134" t="n">
-        <v>11.98</v>
+        <v>21.56</v>
       </c>
       <c r="E134" t="n">
-        <v>718.8</v>
+        <v>1293.6</v>
       </c>
       <c r="F134" t="n">
         <v>0</v>
       </c>
       <c r="G134" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="H134" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I134" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J134" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K134" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L134" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M134" t="n">
-        <v>0</v>
+        <v>0.2307692307692308</v>
       </c>
       <c r="N134" t="n">
         <v>0</v>
       </c>
       <c r="O134" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P134" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q134" t="n">
         <v>0</v>
       </c>
       <c r="R134" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S134" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T134" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U134" t="n">
-        <v>5.167787979966611</v>
+        <v>49.39655844155843</v>
       </c>
       <c r="V134" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W134" t="n">
-        <v>27.78440734557596</v>
+        <v>-8.184355287569575</v>
       </c>
     </row>
     <row r="135">
@@ -10528,71 +10528,71 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>J. BARRA DE LA CRUZ</t>
+          <t>G. HIERRO ABAD</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D135" t="n">
-        <v>23.72</v>
+        <v>11.98</v>
       </c>
       <c r="E135" t="n">
-        <v>1423.2</v>
+        <v>718.8</v>
       </c>
       <c r="F135" t="n">
         <v>0</v>
       </c>
       <c r="G135" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H135" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
       </c>
       <c r="K135" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L135" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M135" t="n">
-        <v>0.5714285714285714</v>
+        <v>0</v>
       </c>
       <c r="N135" t="n">
         <v>0</v>
       </c>
       <c r="O135" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q135" t="n">
         <v>0</v>
       </c>
       <c r="R135" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="S135" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T135" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U135" t="n">
-        <v>24.28193507588533</v>
+        <v>5.167787979966611</v>
       </c>
       <c r="V135" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W135" t="n">
-        <v>24.095434232715</v>
+        <v>27.78440734557596</v>
       </c>
     </row>
     <row r="136">
@@ -10603,26 +10603,26 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>J. MENDOZA ALVAREZ</t>
+          <t>J. BARRA DE LA CRUZ</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D136" t="n">
-        <v>5.98</v>
+        <v>23.72</v>
       </c>
       <c r="E136" t="n">
-        <v>358.8</v>
+        <v>1423.2</v>
       </c>
       <c r="F136" t="n">
         <v>0</v>
       </c>
       <c r="G136" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H136" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I136" t="n">
         <v>1</v>
@@ -10631,19 +10631,19 @@
         <v>0</v>
       </c>
       <c r="K136" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L136" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M136" t="n">
-        <v>0</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="N136" t="n">
         <v>0</v>
       </c>
       <c r="O136" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P136" t="n">
         <v>1</v>
@@ -10652,22 +10652,22 @@
         <v>0</v>
       </c>
       <c r="R136" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="S136" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T136" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U136" t="n">
-        <v>19.02040133779264</v>
+        <v>24.28193507588533</v>
       </c>
       <c r="V136" t="n">
-        <v>-12</v>
+        <v>2</v>
       </c>
       <c r="W136" t="n">
-        <v>-94.45630434782608</v>
+        <v>24.095434232715</v>
       </c>
     </row>
     <row r="137">
@@ -10678,71 +10678,71 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>J. MUNRO</t>
+          <t>J. MENDOZA ALVAREZ</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D137" t="n">
-        <v>23.51</v>
+        <v>5.98</v>
       </c>
       <c r="E137" t="n">
-        <v>1410.6</v>
+        <v>358.8</v>
       </c>
       <c r="F137" t="n">
         <v>0</v>
       </c>
       <c r="G137" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H137" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I137" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J137" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K137" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L137" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M137" t="n">
-        <v>0.625</v>
+        <v>0</v>
       </c>
       <c r="N137" t="n">
         <v>0</v>
       </c>
       <c r="O137" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P137" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q137" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R137" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S137" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T137" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U137" t="n">
-        <v>17.17944704381114</v>
+        <v>19.02040133779264</v>
       </c>
       <c r="V137" t="n">
-        <v>1</v>
+        <v>-12</v>
       </c>
       <c r="W137" t="n">
-        <v>-5.849025946405789</v>
+        <v>-94.45630434782608</v>
       </c>
     </row>
     <row r="138">
@@ -10753,71 +10753,71 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>J. PRATS PEINADO</t>
+          <t>J. MUNRO</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D138" t="n">
-        <v>4.26</v>
+        <v>23.51</v>
       </c>
       <c r="E138" t="n">
-        <v>255.6</v>
+        <v>1410.6</v>
       </c>
       <c r="F138" t="n">
         <v>0</v>
       </c>
       <c r="G138" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H138" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I138" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J138" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K138" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L138" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M138" t="n">
-        <v>0</v>
+        <v>0.625</v>
       </c>
       <c r="N138" t="n">
         <v>0</v>
       </c>
       <c r="O138" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P138" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q138" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R138" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="S138" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T138" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U138" t="n">
-        <v>12.40943661971831</v>
+        <v>17.17944704381114</v>
       </c>
       <c r="V138" t="n">
-        <v>-10</v>
+        <v>1</v>
       </c>
       <c r="W138" t="n">
-        <v>-75.8156338028169</v>
+        <v>-5.849025946405789</v>
       </c>
     </row>
     <row r="139">
@@ -10828,26 +10828,26 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>L. DE LA CRUZ DE LA ROSA</t>
+          <t>J. PRATS PEINADO</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D139" t="n">
-        <v>20.74</v>
+        <v>4.26</v>
       </c>
       <c r="E139" t="n">
-        <v>1244.4</v>
+        <v>255.6</v>
       </c>
       <c r="F139" t="n">
         <v>0</v>
       </c>
       <c r="G139" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H139" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I139" t="n">
         <v>0</v>
@@ -10856,13 +10856,13 @@
         <v>0</v>
       </c>
       <c r="K139" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L139" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M139" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="N139" t="n">
         <v>0</v>
@@ -10871,28 +10871,28 @@
         <v>0</v>
       </c>
       <c r="P139" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q139" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R139" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="S139" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T139" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U139" t="n">
-        <v>21.66678399228544</v>
+        <v>12.40943661971831</v>
       </c>
       <c r="V139" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="W139" t="n">
-        <v>16.53379459980714</v>
+        <v>-75.8156338028169</v>
       </c>
     </row>
     <row r="140">
@@ -10903,26 +10903,26 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>M. ECHEVERRIA FERNANDEZ</t>
+          <t>L. DE LA CRUZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D140" t="n">
-        <v>8.359999999999999</v>
+        <v>20.74</v>
       </c>
       <c r="E140" t="n">
-        <v>501.6</v>
+        <v>1244.4</v>
       </c>
       <c r="F140" t="n">
         <v>0</v>
       </c>
       <c r="G140" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H140" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I140" t="n">
         <v>0</v>
@@ -10931,43 +10931,43 @@
         <v>0</v>
       </c>
       <c r="K140" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L140" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M140" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="N140" t="n">
         <v>0</v>
       </c>
       <c r="O140" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P140" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q140" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R140" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="S140" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T140" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U140" t="n">
-        <v>10.8816028708134</v>
+        <v>21.66678399228544</v>
       </c>
       <c r="V140" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="W140" t="n">
-        <v>-54.19611244019139</v>
+        <v>16.53379459980714</v>
       </c>
     </row>
     <row r="141">
@@ -10978,17 +10978,17 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>M. MANGUE NVOMO</t>
+          <t>M. ECHEVERRIA FERNANDEZ</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D141" t="n">
-        <v>4.37</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="E141" t="n">
-        <v>262.2</v>
+        <v>501.6</v>
       </c>
       <c r="F141" t="n">
         <v>0</v>
@@ -11006,10 +11006,10 @@
         <v>0</v>
       </c>
       <c r="K141" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L141" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M141" t="n">
         <v>0</v>
@@ -11018,31 +11018,31 @@
         <v>0</v>
       </c>
       <c r="O141" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P141" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q141" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R141" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S141" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T141" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U141" t="n">
-        <v>0</v>
+        <v>10.8816028708134</v>
       </c>
       <c r="V141" t="n">
-        <v>3</v>
+        <v>-10</v>
       </c>
       <c r="W141" t="n">
-        <v>23.00434782608696</v>
+        <v>-54.19611244019139</v>
       </c>
     </row>
     <row r="142">
@@ -11053,71 +11053,71 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>M. OILLATAGUERRE</t>
+          <t>M. MANGUE NVOMO</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D142" t="n">
-        <v>24.96</v>
+        <v>4.37</v>
       </c>
       <c r="E142" t="n">
-        <v>1497.6</v>
+        <v>262.2</v>
       </c>
       <c r="F142" t="n">
         <v>0</v>
       </c>
       <c r="G142" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="H142" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I142" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J142" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K142" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L142" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M142" t="n">
-        <v>0.5909090909090909</v>
+        <v>0</v>
       </c>
       <c r="N142" t="n">
         <v>0</v>
       </c>
       <c r="O142" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P142" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q142" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R142" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S142" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T142" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U142" t="n">
-        <v>39.76361778846153</v>
+        <v>0</v>
       </c>
       <c r="V142" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W142" t="n">
-        <v>7.497808493589742</v>
+        <v>23.00434782608696</v>
       </c>
     </row>
     <row r="143">
@@ -11128,41 +11128,41 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>V. FERNANDEZ MORAN</t>
+          <t>M. OILLATAGUERRE</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D143" t="n">
-        <v>21.08</v>
+        <v>24.96</v>
       </c>
       <c r="E143" t="n">
-        <v>1264.8</v>
+        <v>1497.6</v>
       </c>
       <c r="F143" t="n">
         <v>0</v>
       </c>
       <c r="G143" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H143" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I143" t="n">
         <v>4</v>
       </c>
       <c r="J143" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K143" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="L143" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M143" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.5909090909090909</v>
       </c>
       <c r="N143" t="n">
         <v>0</v>
@@ -11171,49 +11171,49 @@
         <v>1</v>
       </c>
       <c r="P143" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q143" t="n">
         <v>1</v>
       </c>
       <c r="R143" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S143" t="n">
         <v>3</v>
       </c>
       <c r="T143" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U143" t="n">
-        <v>24.09317836812145</v>
+        <v>39.76361778846153</v>
       </c>
       <c r="V143" t="n">
-        <v>-12</v>
+        <v>4</v>
       </c>
       <c r="W143" t="n">
-        <v>-28.36280360531309</v>
+        <v>7.497808493589742</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>UROS DE RIVAS</t>
+          <t>RECUCYM BAZU</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>A. BIERSACK LOPEZ</t>
+          <t>V. FERNANDEZ MORAN</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D144" t="n">
-        <v>19.76</v>
+        <v>21.08</v>
       </c>
       <c r="E144" t="n">
-        <v>1185.6</v>
+        <v>1264.8</v>
       </c>
       <c r="F144" t="n">
         <v>0</v>
@@ -11222,52 +11222,52 @@
         <v>9</v>
       </c>
       <c r="H144" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I144" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
       </c>
       <c r="K144" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L144" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M144" t="n">
-        <v>0.5555555555555556</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="N144" t="n">
         <v>0</v>
       </c>
       <c r="O144" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P144" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q144" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R144" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="S144" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T144" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U144" t="n">
-        <v>43.97663461538461</v>
+        <v>24.09317836812145</v>
       </c>
       <c r="V144" t="n">
-        <v>-1</v>
+        <v>-12</v>
       </c>
       <c r="W144" t="n">
-        <v>-2.537788461538461</v>
+        <v>-28.36280360531309</v>
       </c>
     </row>
     <row r="145">
@@ -11278,41 +11278,41 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>A. GARCIA QUILEZ CUERVAS</t>
+          <t>A. BIERSACK LOPEZ</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D145" t="n">
-        <v>12.51</v>
+        <v>24.08</v>
       </c>
       <c r="E145" t="n">
-        <v>750.6</v>
+        <v>1444.8</v>
       </c>
       <c r="F145" t="n">
         <v>0</v>
       </c>
       <c r="G145" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="H145" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I145" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
       </c>
       <c r="K145" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L145" t="n">
         <v>1</v>
       </c>
       <c r="M145" t="n">
-        <v>0.5</v>
+        <v>0.5454545454545454</v>
       </c>
       <c r="N145" t="n">
         <v>0</v>
@@ -11321,28 +11321,28 @@
         <v>0</v>
       </c>
       <c r="P145" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q145" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R145" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="S145" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T145" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U145" t="n">
-        <v>28.06414068745004</v>
+        <v>41.21265365448505</v>
       </c>
       <c r="V145" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="W145" t="n">
-        <v>29.89096722621903</v>
+        <v>-27.52888289036545</v>
       </c>
     </row>
     <row r="146">
@@ -11353,71 +11353,71 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>A. PEREZ CONTI</t>
+          <t>A. GARCIA QUILEZ CUERVAS</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D146" t="n">
-        <v>10.23</v>
+        <v>15.39</v>
       </c>
       <c r="E146" t="n">
-        <v>613.8</v>
+        <v>923.4</v>
       </c>
       <c r="F146" t="n">
         <v>0</v>
       </c>
       <c r="G146" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H146" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I146" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
       </c>
       <c r="K146" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L146" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M146" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="N146" t="n">
         <v>0</v>
       </c>
       <c r="O146" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P146" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q146" t="n">
         <v>0</v>
       </c>
       <c r="R146" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S146" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T146" t="n">
         <v>0</v>
       </c>
       <c r="U146" t="n">
-        <v>13.19992179863148</v>
+        <v>26.55506172839506</v>
       </c>
       <c r="V146" t="n">
-        <v>-15</v>
+        <v>-1</v>
       </c>
       <c r="W146" t="n">
-        <v>-97.54055718475074</v>
+        <v>20.27768680961664</v>
       </c>
     </row>
     <row r="147">
@@ -11428,71 +11428,71 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>C. CRESPO MONTESINOS</t>
+          <t>A. PEREZ CONTI</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D147" t="n">
-        <v>27.52</v>
+        <v>13.21</v>
       </c>
       <c r="E147" t="n">
-        <v>1651.2</v>
+        <v>792.6</v>
       </c>
       <c r="F147" t="n">
         <v>0</v>
       </c>
       <c r="G147" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H147" t="n">
         <v>1</v>
       </c>
       <c r="I147" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
       </c>
       <c r="K147" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L147" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M147" t="n">
-        <v>0.125</v>
+        <v>0.25</v>
       </c>
       <c r="N147" t="n">
         <v>0</v>
       </c>
       <c r="O147" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P147" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q147" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R147" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S147" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T147" t="n">
         <v>1</v>
       </c>
       <c r="U147" t="n">
-        <v>26.72142805232558</v>
+        <v>17.74099924299773</v>
       </c>
       <c r="V147" t="n">
-        <v>-19</v>
+        <v>-16</v>
       </c>
       <c r="W147" t="n">
-        <v>-46.86031250000001</v>
+        <v>-80.08002271006814</v>
       </c>
     </row>
     <row r="148">
@@ -11503,71 +11503,71 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>D. MAGANTO LUCAS</t>
+          <t>C. CRESPO MONTESINOS</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D148" t="n">
-        <v>3.95</v>
+        <v>29.5</v>
       </c>
       <c r="E148" t="n">
-        <v>237</v>
+        <v>1770</v>
       </c>
       <c r="F148" t="n">
         <v>0</v>
       </c>
       <c r="G148" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H148" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I148" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
       </c>
       <c r="K148" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="L148" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M148" t="n">
-        <v>0</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="N148" t="n">
         <v>0</v>
       </c>
       <c r="O148" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P148" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q148" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R148" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="S148" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T148" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U148" t="n">
-        <v>37.7</v>
+        <v>26.27029491525424</v>
       </c>
       <c r="V148" t="n">
-        <v>-4</v>
+        <v>-24</v>
       </c>
       <c r="W148" t="n">
-        <v>-52.36</v>
+        <v>-55.50651525423729</v>
       </c>
     </row>
     <row r="149">
@@ -11578,17 +11578,17 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>D. MARINEZ FERNANDEZ-URRUTIA</t>
+          <t>D. MAGANTO LUCAS</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D149" t="n">
-        <v>8.98</v>
+        <v>3.95</v>
       </c>
       <c r="E149" t="n">
-        <v>538.8</v>
+        <v>237</v>
       </c>
       <c r="F149" t="n">
         <v>0</v>
@@ -11609,7 +11609,7 @@
         <v>2</v>
       </c>
       <c r="L149" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M149" t="n">
         <v>0</v>
@@ -11621,10 +11621,10 @@
         <v>0</v>
       </c>
       <c r="P149" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q149" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R149" t="n">
         <v>0</v>
@@ -11636,13 +11636,13 @@
         <v>0</v>
       </c>
       <c r="U149" t="n">
-        <v>20.21694877505568</v>
+        <v>37.7</v>
       </c>
       <c r="V149" t="n">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="W149" t="n">
-        <v>-1.689710467706016</v>
+        <v>-52.36</v>
       </c>
     </row>
     <row r="150">
@@ -11653,29 +11653,29 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>G. MARTIN LOPEZ-LAGO</t>
+          <t>D. MARINEZ FERNANDEZ-URRUTIA</t>
         </is>
       </c>
       <c r="C150" t="n">
         <v>4</v>
       </c>
       <c r="D150" t="n">
-        <v>7.75</v>
+        <v>10.86</v>
       </c>
       <c r="E150" t="n">
-        <v>465</v>
+        <v>651.6</v>
       </c>
       <c r="F150" t="n">
         <v>0</v>
       </c>
       <c r="G150" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H150" t="n">
         <v>0</v>
       </c>
       <c r="I150" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -11696,28 +11696,28 @@
         <v>0</v>
       </c>
       <c r="P150" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q150" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R150" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S150" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T150" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U150" t="n">
-        <v>31.9995870967742</v>
+        <v>16.71714548802947</v>
       </c>
       <c r="V150" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="W150" t="n">
-        <v>-65.43291612903226</v>
+        <v>-38.64232044198896</v>
       </c>
     </row>
     <row r="151">
@@ -11728,29 +11728,29 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>M. VILLAMANDOS TORRES</t>
+          <t>G. MARTIN LOPEZ-LAGO</t>
         </is>
       </c>
       <c r="C151" t="n">
         <v>5</v>
       </c>
       <c r="D151" t="n">
-        <v>8.870000000000001</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="E151" t="n">
-        <v>532.2</v>
+        <v>583.2</v>
       </c>
       <c r="F151" t="n">
         <v>0</v>
       </c>
       <c r="G151" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I151" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -11759,10 +11759,10 @@
         <v>2</v>
       </c>
       <c r="L151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M151" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="N151" t="n">
         <v>0</v>
@@ -11777,22 +11777,22 @@
         <v>0</v>
       </c>
       <c r="R151" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U151" t="n">
-        <v>14.75662908680947</v>
+        <v>33.62106995884773</v>
       </c>
       <c r="V151" t="n">
-        <v>-3</v>
+        <v>-12</v>
       </c>
       <c r="W151" t="n">
-        <v>-51.03695603156707</v>
+        <v>-80.50120370370369</v>
       </c>
     </row>
     <row r="152">
@@ -11803,23 +11803,23 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>O. HADI ADEGBITE</t>
+          <t>M. VILLAMANDOS TORRES</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D152" t="n">
-        <v>3.22</v>
+        <v>8.870000000000001</v>
       </c>
       <c r="E152" t="n">
-        <v>193.2</v>
+        <v>532.2</v>
       </c>
       <c r="F152" t="n">
         <v>0</v>
       </c>
       <c r="G152" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H152" t="n">
         <v>0</v>
@@ -11861,13 +11861,13 @@
         <v>0</v>
       </c>
       <c r="U152" t="n">
-        <v>70.46260869565218</v>
+        <v>14.75662908680947</v>
       </c>
       <c r="V152" t="n">
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="W152" t="n">
-        <v>-62.39506211180125</v>
+        <v>-51.03695603156707</v>
       </c>
     </row>
     <row r="153">
@@ -11878,41 +11878,41 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>O. MENDEZ BLANCO</t>
+          <t>O. HADI ADEGBITE</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D153" t="n">
-        <v>1.95</v>
+        <v>4.7</v>
       </c>
       <c r="E153" t="n">
-        <v>117</v>
+        <v>282</v>
       </c>
       <c r="F153" t="n">
         <v>0</v>
       </c>
       <c r="G153" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H153" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I153" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J153" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K153" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L153" t="n">
         <v>0</v>
       </c>
       <c r="M153" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="N153" t="n">
         <v>0</v>
@@ -11921,7 +11921,7 @@
         <v>0</v>
       </c>
       <c r="P153" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q153" t="n">
         <v>0</v>
@@ -11936,13 +11936,13 @@
         <v>0</v>
       </c>
       <c r="U153" t="n">
-        <v>40.98</v>
+        <v>48.2743829787234</v>
       </c>
       <c r="V153" t="n">
-        <v>3</v>
+        <v>-7</v>
       </c>
       <c r="W153" t="n">
-        <v>61.48</v>
+        <v>-88.75321276595744</v>
       </c>
     </row>
     <row r="154">
@@ -11953,71 +11953,71 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>P. ESTEBANEZ GONZALEZ</t>
+          <t>O. MENDEZ BLANCO</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D154" t="n">
-        <v>24.39</v>
+        <v>5.72</v>
       </c>
       <c r="E154" t="n">
-        <v>1463.4</v>
+        <v>343.2</v>
       </c>
       <c r="F154" t="n">
         <v>0</v>
       </c>
       <c r="G154" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H154" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I154" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J154" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K154" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L154" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M154" t="n">
-        <v>0.4</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="N154" t="n">
         <v>0</v>
       </c>
       <c r="O154" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P154" t="n">
         <v>0</v>
       </c>
       <c r="Q154" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R154" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S154" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T154" t="n">
         <v>0</v>
       </c>
       <c r="U154" t="n">
-        <v>31.36233702337024</v>
+        <v>46.925</v>
       </c>
       <c r="V154" t="n">
-        <v>-9</v>
+        <v>0</v>
       </c>
       <c r="W154" t="n">
-        <v>-22.87690856908569</v>
+        <v>-9.767727272727273</v>
       </c>
     </row>
     <row r="155">
@@ -12028,41 +12028,41 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>P. ROSSI</t>
+          <t>P. ESTEBANEZ GONZALEZ</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D155" t="n">
-        <v>20.74</v>
+        <v>27.46</v>
       </c>
       <c r="E155" t="n">
-        <v>1244.4</v>
+        <v>1647.6</v>
       </c>
       <c r="F155" t="n">
         <v>0</v>
       </c>
       <c r="G155" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="H155" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I155" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
       </c>
       <c r="K155" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L155" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M155" t="n">
-        <v>0</v>
+        <v>0.3636363636363636</v>
       </c>
       <c r="N155" t="n">
         <v>0</v>
@@ -12074,25 +12074,25 @@
         <v>0</v>
       </c>
       <c r="Q155" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R155" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="S155" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T155" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U155" t="n">
-        <v>9.514754098360655</v>
+        <v>29.45366715222141</v>
       </c>
       <c r="V155" t="n">
-        <v>-8</v>
+        <v>-10</v>
       </c>
       <c r="W155" t="n">
-        <v>-30.19399710703953</v>
+        <v>-22.52285142024763</v>
       </c>
     </row>
     <row r="156">
@@ -12103,38 +12103,38 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>P. TOMICO RUIZ</t>
+          <t>P. ROSSI</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D156" t="n">
-        <v>0.05</v>
+        <v>20.74</v>
       </c>
       <c r="E156" t="n">
-        <v>3</v>
+        <v>1244.4</v>
       </c>
       <c r="F156" t="n">
         <v>0</v>
       </c>
       <c r="G156" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H156" t="n">
         <v>0</v>
       </c>
       <c r="I156" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
       </c>
       <c r="K156" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L156" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M156" t="n">
         <v>0</v>
@@ -12152,22 +12152,22 @@
         <v>0</v>
       </c>
       <c r="R156" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S156" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T156" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U156" t="n">
-        <v>0</v>
+        <v>9.514754098360655</v>
       </c>
       <c r="V156" t="n">
-        <v>-2</v>
+        <v>-8</v>
       </c>
       <c r="W156" t="n">
-        <v>0</v>
+        <v>-30.19399710703953</v>
       </c>
     </row>
     <row r="157">
@@ -12178,7 +12178,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>S. PARADELA PARIS</t>
+          <t>P. TOMICO RUIZ</t>
         </is>
       </c>
       <c r="C157" t="n">
@@ -12248,76 +12248,76 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>ZENTRO BASKET MADRID</t>
+          <t>UROS DE RIVAS</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>B. SCHUCH</t>
+          <t>S. PARADELA PARIS</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D158" t="n">
-        <v>38.9</v>
+        <v>0.05</v>
       </c>
       <c r="E158" t="n">
-        <v>2334</v>
+        <v>3</v>
       </c>
       <c r="F158" t="n">
         <v>0</v>
       </c>
       <c r="G158" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="H158" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I158" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
       </c>
       <c r="K158" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L158" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M158" t="n">
-        <v>0.1818181818181818</v>
+        <v>0</v>
       </c>
       <c r="N158" t="n">
         <v>0</v>
       </c>
       <c r="O158" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P158" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q158" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R158" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="S158" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="T158" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="U158" t="n">
-        <v>25.52301285347044</v>
+        <v>0</v>
       </c>
       <c r="V158" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="W158" t="n">
-        <v>14.99595372750643</v>
+        <v>0</v>
       </c>
     </row>
     <row r="159">
@@ -12328,23 +12328,23 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>D. VAL GUTIERREZ</t>
+          <t>B. SCHUCH</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D159" t="n">
-        <v>21.17</v>
+        <v>38.9</v>
       </c>
       <c r="E159" t="n">
-        <v>1270.2</v>
+        <v>2334</v>
       </c>
       <c r="F159" t="n">
         <v>0</v>
       </c>
       <c r="G159" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H159" t="n">
         <v>2</v>
@@ -12353,46 +12353,46 @@
         <v>8</v>
       </c>
       <c r="J159" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K159" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L159" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M159" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.1818181818181818</v>
       </c>
       <c r="N159" t="n">
         <v>0</v>
       </c>
       <c r="O159" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P159" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Q159" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R159" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="S159" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="T159" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U159" t="n">
-        <v>30.69956542276807</v>
+        <v>25.52301285347044</v>
       </c>
       <c r="V159" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="W159" t="n">
-        <v>28.35527161076996</v>
+        <v>14.99595372750643</v>
       </c>
     </row>
     <row r="160">
@@ -12403,41 +12403,41 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>F. MORENO GUTIERREZ</t>
+          <t>D. VAL GUTIERREZ</t>
         </is>
       </c>
       <c r="C160" t="n">
         <v>5</v>
       </c>
       <c r="D160" t="n">
-        <v>6.800000000000001</v>
+        <v>21.17</v>
       </c>
       <c r="E160" t="n">
-        <v>408</v>
+        <v>1270.2</v>
       </c>
       <c r="F160" t="n">
         <v>0</v>
       </c>
       <c r="G160" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H160" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I160" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J160" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K160" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L160" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M160" t="n">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="N160" t="n">
         <v>0</v>
@@ -12452,22 +12452,22 @@
         <v>1</v>
       </c>
       <c r="R160" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S160" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T160" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U160" t="n">
-        <v>14.60823529411765</v>
+        <v>30.69956542276807</v>
       </c>
       <c r="V160" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W160" t="n">
-        <v>21.02470588235294</v>
+        <v>28.35527161076996</v>
       </c>
     </row>
     <row r="161">
@@ -12478,17 +12478,17 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>G. FATA ALCARAZ</t>
+          <t>F. MORENO GUTIERREZ</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D161" t="n">
-        <v>1.37</v>
+        <v>6.800000000000001</v>
       </c>
       <c r="E161" t="n">
-        <v>82.2</v>
+        <v>408</v>
       </c>
       <c r="F161" t="n">
         <v>0</v>
@@ -12521,10 +12521,10 @@
         <v>0</v>
       </c>
       <c r="P161" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q161" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R161" t="n">
         <v>1</v>
@@ -12536,13 +12536,13 @@
         <v>1</v>
       </c>
       <c r="U161" t="n">
-        <v>25.77</v>
+        <v>14.60823529411765</v>
       </c>
       <c r="V161" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="W161" t="n">
-        <v>42.6</v>
+        <v>21.02470588235294</v>
       </c>
     </row>
     <row r="162">
@@ -12553,71 +12553,71 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>G. GOMA</t>
+          <t>G. FATA ALCARAZ</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D162" t="n">
-        <v>44.14</v>
+        <v>1.37</v>
       </c>
       <c r="E162" t="n">
-        <v>2648.4</v>
+        <v>82.2</v>
       </c>
       <c r="F162" t="n">
         <v>0</v>
       </c>
       <c r="G162" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="H162" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I162" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
       </c>
       <c r="K162" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="L162" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M162" t="n">
-        <v>0.4444444444444444</v>
+        <v>0</v>
       </c>
       <c r="N162" t="n">
         <v>0</v>
       </c>
       <c r="O162" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P162" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q162" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R162" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="S162" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="T162" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="U162" t="n">
-        <v>31.78287267784323</v>
+        <v>25.77</v>
       </c>
       <c r="V162" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="W162" t="n">
-        <v>18.58798595378342</v>
+        <v>42.6</v>
       </c>
     </row>
     <row r="163">
@@ -12628,71 +12628,71 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>G. TCHIRAKADZE</t>
+          <t>G. GOMA</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D163" t="n">
-        <v>9.26</v>
+        <v>44.14</v>
       </c>
       <c r="E163" t="n">
-        <v>555.6</v>
+        <v>2648.4</v>
       </c>
       <c r="F163" t="n">
         <v>0</v>
       </c>
       <c r="G163" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="H163" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I163" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
       </c>
       <c r="K163" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="L163" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M163" t="n">
-        <v>0</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="N163" t="n">
         <v>0</v>
       </c>
       <c r="O163" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P163" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q163" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R163" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="S163" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="T163" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U163" t="n">
-        <v>0</v>
+        <v>31.78287267784323</v>
       </c>
       <c r="V163" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="W163" t="n">
-        <v>5.526889848812099</v>
+        <v>18.58798595378342</v>
       </c>
     </row>
     <row r="164">
@@ -12703,71 +12703,71 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>J. VAQUERO PASCUAL</t>
+          <t>G. TCHIRAKADZE</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D164" t="n">
-        <v>14.88</v>
+        <v>9.26</v>
       </c>
       <c r="E164" t="n">
-        <v>892.8</v>
+        <v>555.6</v>
       </c>
       <c r="F164" t="n">
         <v>0</v>
       </c>
       <c r="G164" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H164" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I164" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
       </c>
       <c r="K164" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L164" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M164" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="N164" t="n">
         <v>0</v>
       </c>
       <c r="O164" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P164" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q164" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R164" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S164" t="n">
         <v>1</v>
       </c>
       <c r="T164" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U164" t="n">
-        <v>55.41617607526882</v>
+        <v>0</v>
       </c>
       <c r="V164" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="W164" t="n">
-        <v>42.46101478494624</v>
+        <v>5.526889848812099</v>
       </c>
     </row>
     <row r="165">
@@ -12778,71 +12778,71 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>L. SCHIEBELHUT LUIS</t>
+          <t>J. VAQUERO PASCUAL</t>
         </is>
       </c>
       <c r="C165" t="n">
+        <v>6</v>
+      </c>
+      <c r="D165" t="n">
+        <v>14.88</v>
+      </c>
+      <c r="E165" t="n">
+        <v>892.8</v>
+      </c>
+      <c r="F165" t="n">
+        <v>0</v>
+      </c>
+      <c r="G165" t="n">
+        <v>10</v>
+      </c>
+      <c r="H165" t="n">
+        <v>3</v>
+      </c>
+      <c r="I165" t="n">
+        <v>4</v>
+      </c>
+      <c r="J165" t="n">
+        <v>0</v>
+      </c>
+      <c r="K165" t="n">
+        <v>8</v>
+      </c>
+      <c r="L165" t="n">
+        <v>7</v>
+      </c>
+      <c r="M165" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="N165" t="n">
+        <v>0</v>
+      </c>
+      <c r="O165" t="n">
+        <v>1</v>
+      </c>
+      <c r="P165" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q165" t="n">
+        <v>3</v>
+      </c>
+      <c r="R165" t="n">
+        <v>2</v>
+      </c>
+      <c r="S165" t="n">
+        <v>1</v>
+      </c>
+      <c r="T165" t="n">
+        <v>1</v>
+      </c>
+      <c r="U165" t="n">
+        <v>55.41617607526882</v>
+      </c>
+      <c r="V165" t="n">
         <v>9</v>
       </c>
-      <c r="D165" t="n">
-        <v>31.89</v>
-      </c>
-      <c r="E165" t="n">
-        <v>1913.4</v>
-      </c>
-      <c r="F165" t="n">
-        <v>0</v>
-      </c>
-      <c r="G165" t="n">
-        <v>8</v>
-      </c>
-      <c r="H165" t="n">
-        <v>1</v>
-      </c>
-      <c r="I165" t="n">
-        <v>5</v>
-      </c>
-      <c r="J165" t="n">
-        <v>1</v>
-      </c>
-      <c r="K165" t="n">
-        <v>0</v>
-      </c>
-      <c r="L165" t="n">
-        <v>0</v>
-      </c>
-      <c r="M165" t="n">
-        <v>0.1875</v>
-      </c>
-      <c r="N165" t="n">
-        <v>0</v>
-      </c>
-      <c r="O165" t="n">
-        <v>0</v>
-      </c>
-      <c r="P165" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q165" t="n">
-        <v>0</v>
-      </c>
-      <c r="R165" t="n">
-        <v>3</v>
-      </c>
-      <c r="S165" t="n">
-        <v>3</v>
-      </c>
-      <c r="T165" t="n">
-        <v>0</v>
-      </c>
-      <c r="U165" t="n">
-        <v>18.84556914393226</v>
-      </c>
-      <c r="V165" t="n">
-        <v>-3</v>
-      </c>
       <c r="W165" t="n">
-        <v>7.258601442458453</v>
+        <v>42.46101478494624</v>
       </c>
     </row>
     <row r="166">
@@ -12853,71 +12853,71 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>M. ESTAPE ROIZ</t>
+          <t>L. SCHIEBELHUT LUIS</t>
         </is>
       </c>
       <c r="C166" t="n">
         <v>9</v>
       </c>
       <c r="D166" t="n">
-        <v>33.96</v>
+        <v>31.89</v>
       </c>
       <c r="E166" t="n">
-        <v>2037.6</v>
+        <v>1913.4</v>
       </c>
       <c r="F166" t="n">
         <v>0</v>
       </c>
       <c r="G166" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="H166" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I166" t="n">
         <v>5</v>
       </c>
       <c r="J166" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K166" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L166" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M166" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.1875</v>
       </c>
       <c r="N166" t="n">
         <v>0</v>
       </c>
       <c r="O166" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P166" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q166" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R166" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S166" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T166" t="n">
         <v>0</v>
       </c>
       <c r="U166" t="n">
-        <v>31.48195229681979</v>
+        <v>18.84556914393226</v>
       </c>
       <c r="V166" t="n">
-        <v>9</v>
+        <v>-3</v>
       </c>
       <c r="W166" t="n">
-        <v>15.29616018845701</v>
+        <v>7.258601442458453</v>
       </c>
     </row>
     <row r="167">
@@ -12928,53 +12928,53 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>M. RUBIO CORCHADO</t>
+          <t>M. ESTAPE ROIZ</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D167" t="n">
-        <v>2.92</v>
+        <v>33.96</v>
       </c>
       <c r="E167" t="n">
-        <v>175.2</v>
+        <v>2037.6</v>
       </c>
       <c r="F167" t="n">
         <v>0</v>
       </c>
       <c r="G167" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="H167" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I167" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J167" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K167" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L167" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M167" t="n">
-        <v>0</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="N167" t="n">
         <v>0</v>
       </c>
       <c r="O167" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P167" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q167" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R167" t="n">
         <v>1</v>
@@ -12986,13 +12986,13 @@
         <v>0</v>
       </c>
       <c r="U167" t="n">
-        <v>12.89</v>
+        <v>31.48195229681979</v>
       </c>
       <c r="V167" t="n">
-        <v>-5</v>
+        <v>9</v>
       </c>
       <c r="W167" t="n">
-        <v>-95.75</v>
+        <v>15.29616018845701</v>
       </c>
     </row>
     <row r="168">
@@ -13003,17 +13003,17 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>N. VIÑO LOPEZ</t>
+          <t>M. RUBIO CORCHADO</t>
         </is>
       </c>
       <c r="C168" t="n">
         <v>1</v>
       </c>
       <c r="D168" t="n">
-        <v>4.5</v>
+        <v>2.92</v>
       </c>
       <c r="E168" t="n">
-        <v>270</v>
+        <v>175.2</v>
       </c>
       <c r="F168" t="n">
         <v>0</v>
@@ -13022,7 +13022,7 @@
         <v>1</v>
       </c>
       <c r="H168" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I168" t="n">
         <v>0</v>
@@ -13037,37 +13037,37 @@
         <v>0</v>
       </c>
       <c r="M168" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N168" t="n">
         <v>0</v>
       </c>
       <c r="O168" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P168" t="n">
         <v>0</v>
       </c>
       <c r="Q168" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R168" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S168" t="n">
         <v>1</v>
       </c>
       <c r="T168" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U168" t="n">
-        <v>15.53</v>
+        <v>12.89</v>
       </c>
       <c r="V168" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="W168" t="n">
-        <v>8.199999999999999</v>
+        <v>-95.75</v>
       </c>
     </row>
     <row r="169">
@@ -13078,26 +13078,26 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>S. COULIBALY</t>
+          <t>N. VIÑO LOPEZ</t>
         </is>
       </c>
       <c r="C169" t="n">
         <v>1</v>
       </c>
       <c r="D169" t="n">
-        <v>0.43</v>
+        <v>4.5</v>
       </c>
       <c r="E169" t="n">
-        <v>25.8</v>
+        <v>270</v>
       </c>
       <c r="F169" t="n">
         <v>0</v>
       </c>
       <c r="G169" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H169" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I169" t="n">
         <v>0</v>
@@ -13112,37 +13112,37 @@
         <v>0</v>
       </c>
       <c r="M169" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N169" t="n">
         <v>0</v>
       </c>
       <c r="O169" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P169" t="n">
         <v>0</v>
       </c>
       <c r="Q169" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R169" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S169" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T169" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U169" t="n">
-        <v>0</v>
+        <v>15.53</v>
       </c>
       <c r="V169" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W169" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="170">
@@ -13153,70 +13153,145 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
+          <t>S. COULIBALY</t>
+        </is>
+      </c>
+      <c r="C170" t="n">
+        <v>1</v>
+      </c>
+      <c r="D170" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="E170" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="F170" t="n">
+        <v>0</v>
+      </c>
+      <c r="G170" t="n">
+        <v>0</v>
+      </c>
+      <c r="H170" t="n">
+        <v>0</v>
+      </c>
+      <c r="I170" t="n">
+        <v>0</v>
+      </c>
+      <c r="J170" t="n">
+        <v>0</v>
+      </c>
+      <c r="K170" t="n">
+        <v>0</v>
+      </c>
+      <c r="L170" t="n">
+        <v>0</v>
+      </c>
+      <c r="M170" t="n">
+        <v>0</v>
+      </c>
+      <c r="N170" t="n">
+        <v>0</v>
+      </c>
+      <c r="O170" t="n">
+        <v>0</v>
+      </c>
+      <c r="P170" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q170" t="n">
+        <v>0</v>
+      </c>
+      <c r="R170" t="n">
+        <v>0</v>
+      </c>
+      <c r="S170" t="n">
+        <v>0</v>
+      </c>
+      <c r="T170" t="n">
+        <v>0</v>
+      </c>
+      <c r="U170" t="n">
+        <v>0</v>
+      </c>
+      <c r="V170" t="n">
+        <v>0</v>
+      </c>
+      <c r="W170" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>ZENTRO BASKET MADRID</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
           <t>T. VERDERA BENASSAR</t>
         </is>
       </c>
-      <c r="C170" t="n">
+      <c r="C171" t="n">
         <v>7</v>
       </c>
-      <c r="D170" t="n">
+      <c r="D171" t="n">
         <v>14.15</v>
       </c>
-      <c r="E170" t="n">
+      <c r="E171" t="n">
         <v>849</v>
       </c>
-      <c r="F170" t="n">
-        <v>0</v>
-      </c>
-      <c r="G170" t="n">
+      <c r="F171" t="n">
+        <v>0</v>
+      </c>
+      <c r="G171" t="n">
         <v>9</v>
       </c>
-      <c r="H170" t="n">
-        <v>1</v>
-      </c>
-      <c r="I170" t="n">
-        <v>2</v>
-      </c>
-      <c r="J170" t="n">
-        <v>0</v>
-      </c>
-      <c r="K170" t="n">
-        <v>0</v>
-      </c>
-      <c r="L170" t="n">
-        <v>0</v>
-      </c>
-      <c r="M170" t="n">
+      <c r="H171" t="n">
+        <v>1</v>
+      </c>
+      <c r="I171" t="n">
+        <v>2</v>
+      </c>
+      <c r="J171" t="n">
+        <v>0</v>
+      </c>
+      <c r="K171" t="n">
+        <v>0</v>
+      </c>
+      <c r="L171" t="n">
+        <v>0</v>
+      </c>
+      <c r="M171" t="n">
         <v>0.1111111111111111</v>
       </c>
-      <c r="N170" t="n">
-        <v>0</v>
-      </c>
-      <c r="O170" t="n">
-        <v>1</v>
-      </c>
-      <c r="P170" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q170" t="n">
-        <v>1</v>
-      </c>
-      <c r="R170" t="n">
-        <v>3</v>
-      </c>
-      <c r="S170" t="n">
-        <v>2</v>
-      </c>
-      <c r="T170" t="n">
-        <v>1</v>
-      </c>
-      <c r="U170" t="n">
+      <c r="N171" t="n">
+        <v>0</v>
+      </c>
+      <c r="O171" t="n">
+        <v>1</v>
+      </c>
+      <c r="P171" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q171" t="n">
+        <v>1</v>
+      </c>
+      <c r="R171" t="n">
+        <v>3</v>
+      </c>
+      <c r="S171" t="n">
+        <v>2</v>
+      </c>
+      <c r="T171" t="n">
+        <v>1</v>
+      </c>
+      <c r="U171" t="n">
         <v>39.98686925795053</v>
       </c>
-      <c r="V170" t="n">
-        <v>4</v>
-      </c>
-      <c r="W170" t="n">
+      <c r="V171" t="n">
+        <v>4</v>
+      </c>
+      <c r="W171" t="n">
         <v>21.68115194346289</v>
       </c>
     </row>
